--- a/VerveStacks_ESP/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ESP/ReportDefs_vervestacks.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B57AB34-5327-4613-BD06-2FC1B690AD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFA3B6F-77C9-4026-A7F7-2B3175ECC1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
-    <sheet name="TS_Defs" sheetId="27" r:id="rId2"/>
-    <sheet name="TS_ratios" sheetId="68" r:id="rId3"/>
-    <sheet name="Sankey" sheetId="69" r:id="rId4"/>
-    <sheet name="PSet_MAP" sheetId="57" r:id="rId5"/>
-    <sheet name="CSET_MAP" sheetId="66" r:id="rId6"/>
-    <sheet name="CName_MAP" sheetId="58" r:id="rId7"/>
-    <sheet name="timeslice map" sheetId="64" r:id="rId8"/>
-    <sheet name="process map" sheetId="65" r:id="rId9"/>
-    <sheet name="commodity map" sheetId="67" r:id="rId10"/>
-    <sheet name="ATS" sheetId="63" r:id="rId11"/>
-    <sheet name="UnitConv" sheetId="59" r:id="rId12"/>
+    <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
+    <sheet name="ScenMap" sheetId="56" r:id="rId2"/>
+    <sheet name="TS_Defs" sheetId="27" r:id="rId3"/>
+    <sheet name="TS_ratios" sheetId="68" r:id="rId4"/>
+    <sheet name="Sankey" sheetId="69" r:id="rId5"/>
+    <sheet name="PSet_MAP" sheetId="57" r:id="rId6"/>
+    <sheet name="CSET_MAP" sheetId="66" r:id="rId7"/>
+    <sheet name="CName_MAP" sheetId="58" r:id="rId8"/>
+    <sheet name="timeslice map" sheetId="64" r:id="rId9"/>
+    <sheet name="process map" sheetId="65" r:id="rId10"/>
+    <sheet name="commodity map" sheetId="67" r:id="rId11"/>
+    <sheet name="ATS" sheetId="63" r:id="rId12"/>
+    <sheet name="UnitConv" sheetId="59" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TS_Defs!$A$2:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TS_Defs!$A$2:$N$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="388">
   <si>
     <t>Unit</t>
   </si>
@@ -212,9 +213,6 @@
     <t>Power</t>
   </si>
   <si>
-    <t>MEuro05</t>
-  </si>
-  <si>
     <t>group_by</t>
   </si>
   <si>
@@ -458,45 +456,9 @@
     <t>old</t>
   </si>
   <si>
-    <t>vstacks_t1~</t>
-  </si>
-  <si>
-    <t>vstacks_t5~</t>
-  </si>
-  <si>
-    <t>vstacks_w2~</t>
-  </si>
-  <si>
-    <t>ngfs</t>
-  </si>
-  <si>
     <t>timeslice</t>
   </si>
   <si>
-    <t>Low demand</t>
-  </si>
-  <si>
-    <t>Fragmented World</t>
-  </si>
-  <si>
-    <t>3 days</t>
-  </si>
-  <si>
-    <t>15 days</t>
-  </si>
-  <si>
-    <t>2 weeks</t>
-  </si>
-  <si>
-    <t>_3d</t>
-  </si>
-  <si>
-    <t>_15d</t>
-  </si>
-  <si>
-    <t>_2w</t>
-  </si>
-  <si>
     <t>CO2</t>
   </si>
   <si>
@@ -536,9 +498,6 @@
     <t>gas</t>
   </si>
   <si>
-    <t>co2captured</t>
-  </si>
-  <si>
     <t>*ccs-rf</t>
   </si>
   <si>
@@ -596,39 +555,15 @@
     <t>~Timeslice_Map</t>
   </si>
   <si>
-    <t>vstacks_ts16~</t>
-  </si>
-  <si>
-    <t>vstacks_t_annual~</t>
-  </si>
-  <si>
-    <t>ts-16</t>
-  </si>
-  <si>
-    <t>ts-annual</t>
-  </si>
-  <si>
-    <t>_16</t>
-  </si>
-  <si>
-    <t>_ann</t>
-  </si>
-  <si>
     <t>-ElcAgg*,-*EV*,-g[_]*</t>
   </si>
   <si>
-    <t>ELC,ELC_???-???,e[_]*</t>
-  </si>
-  <si>
     <t>T_neg_andor</t>
   </si>
   <si>
     <t>downscale_option</t>
   </si>
   <si>
-    <t>~TS_Defs: Snk_attr=Grid Flows</t>
-  </si>
-  <si>
     <t>TWh</t>
   </si>
   <si>
@@ -839,19 +774,478 @@
     <t>Transformers Up</t>
   </si>
   <si>
-    <t>Declared NDCs</t>
-  </si>
-  <si>
-    <t>Limited to 2 deg</t>
-  </si>
-  <si>
-    <t>Postponed Transition</t>
-  </si>
-  <si>
-    <t>Target Net Zero 2050</t>
-  </si>
-  <si>
-    <t>Current Policies</t>
+    <t>s1p1v1_d</t>
+  </si>
+  <si>
+    <t>s3p3v3_d</t>
+  </si>
+  <si>
+    <t>s2_w</t>
+  </si>
+  <si>
+    <t>s2_w_p2_d</t>
+  </si>
+  <si>
+    <t>ts12_clu</t>
+  </si>
+  <si>
+    <t>ts24_clu</t>
+  </si>
+  <si>
+    <t>ts48_clu</t>
+  </si>
+  <si>
+    <t>s5p5v5_d</t>
+  </si>
+  <si>
+    <t>ts_annual</t>
+  </si>
+  <si>
+    <t>ts_12</t>
+  </si>
+  <si>
+    <t>a2w2d</t>
+  </si>
+  <si>
+    <t>d9d</t>
+  </si>
+  <si>
+    <t>b2w</t>
+  </si>
+  <si>
+    <t>c15d</t>
+  </si>
+  <si>
+    <t>e3d</t>
+  </si>
+  <si>
+    <t>fTS48c</t>
+  </si>
+  <si>
+    <t>gTS24c</t>
+  </si>
+  <si>
+    <t>hTS12c</t>
+  </si>
+  <si>
+    <t>iTS12</t>
+  </si>
+  <si>
+    <t>jAnn</t>
+  </si>
+  <si>
+    <t>Limit warming to 1.5°C (&gt;50%) with no or limited overshoot</t>
+  </si>
+  <si>
+    <t>Limit warming to 1.5°C (&gt;67%) with high overshoot</t>
+  </si>
+  <si>
+    <t>Limit warming to 2°C (&gt;67%) with higher action post-2030</t>
+  </si>
+  <si>
+    <t>Limit warming to 2°C (&gt;50%) with immediate action</t>
+  </si>
+  <si>
+    <t>Likely above 3°C warming with limited mitigation</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%)</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%)</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS</t>
+  </si>
+  <si>
+    <t>a 3 deg</t>
+  </si>
+  <si>
+    <t>ar6_r10</t>
+  </si>
+  <si>
+    <t>ELC,ELC_???-???*,e[_]*</t>
+  </si>
+  <si>
+    <t>*ccs</t>
+  </si>
+  <si>
+    <t>s1_d</t>
+  </si>
+  <si>
+    <t>f3d</t>
+  </si>
+  <si>
+    <t>~TS_Defs: Snk_attr=SANKEY whole system</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>windon</t>
+  </si>
+  <si>
+    <t>windoff</t>
+  </si>
+  <si>
+    <t>wind onshore</t>
+  </si>
+  <si>
+    <t>wind offshore</t>
+  </si>
+  <si>
+    <t>&lt;gen_cname&gt;_src_&lt;gen_pname&gt;</t>
+  </si>
+  <si>
+    <t>&lt;gen_cname&gt;_snk_&lt;pset&gt;</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Hydrogen</t>
+  </si>
+  <si>
+    <t>&lt;gen_cname&gt;_snk_&lt;gen_pname&gt;</t>
+  </si>
+  <si>
+    <t>Fuels</t>
+  </si>
+  <si>
+    <t>Onshore Wind</t>
+  </si>
+  <si>
+    <t>Offshore Wind</t>
+  </si>
+  <si>
+    <t>&lt;cset&gt;_src_&lt;pset&gt;</t>
+  </si>
+  <si>
+    <t>&lt;cset&gt;_snk_&lt;pset&gt;</t>
+  </si>
+  <si>
+    <t>&lt;cset&gt;_snk_&lt;gen_pname&gt;</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>Reg_wobj</t>
+  </si>
+  <si>
+    <t>Reg_ACost</t>
+  </si>
+  <si>
+    <t>m$2020</t>
+  </si>
+  <si>
+    <t>SysCost_NPV</t>
+  </si>
+  <si>
+    <t>SysCost_Annual</t>
+  </si>
+  <si>
+    <t>DeACT TS_Defs: Snk_attr=SANKEY Grid Flows</t>
+  </si>
+  <si>
+    <t>~Scenmap</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>scen</t>
+  </si>
+  <si>
+    <t>case_no</t>
+  </si>
+  <si>
+    <t>climate</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.kAnn</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.kAnn</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).kAnn</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).kAnn</t>
+  </si>
+  <si>
+    <t>a 3 deg.kAnn</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.k12</t>
+  </si>
+  <si>
+    <t>ts_12t</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.k12</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).k12</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).k12</t>
+  </si>
+  <si>
+    <t>a 3 deg.k12</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.j12</t>
+  </si>
+  <si>
+    <t>ts_012</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.j12</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).j12</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).j12</t>
+  </si>
+  <si>
+    <t>a 3 deg.j12</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.i24</t>
+  </si>
+  <si>
+    <t>ts_024</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.i24</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).i24</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).i24</t>
+  </si>
+  <si>
+    <t>a 3 deg.i24</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.h48</t>
+  </si>
+  <si>
+    <t>ts_048</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.h48</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).h48</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).h48</t>
+  </si>
+  <si>
+    <t>a 3 deg.h48</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.g64</t>
+  </si>
+  <si>
+    <t>ts_064</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.g64</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).g64</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).g64</t>
+  </si>
+  <si>
+    <t>a 3 deg.g64</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.f97p50</t>
+  </si>
+  <si>
+    <t>ts_096P50</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.f97p50</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).f97p50</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).f97p50</t>
+  </si>
+  <si>
+    <t>a 3 deg.f97p50</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.f96p10</t>
+  </si>
+  <si>
+    <t>ts_096P10</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.f96p10</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).f96p10</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).f96p10</t>
+  </si>
+  <si>
+    <t>a 3 deg.f96p10</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.f96p90</t>
+  </si>
+  <si>
+    <t>ts_096P90</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.f96p90</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).f96p90</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).f96p90</t>
+  </si>
+  <si>
+    <t>a 3 deg.f96p90</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.e3d</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.e3d</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).e3d</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).e3d</t>
+  </si>
+  <si>
+    <t>a 3 deg.e3d</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.d9d</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.d9d</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).d9d</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).d9d</t>
+  </si>
+  <si>
+    <t>a 3 deg.d9d</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.c15d</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.c15d</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).c15d</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).c15d</t>
+  </si>
+  <si>
+    <t>a 3 deg.c15d</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.b2w</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.b2w</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).b2w</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).b2w</t>
+  </si>
+  <si>
+    <t>a 3 deg.b2w</t>
+  </si>
+  <si>
+    <t>e 1.5 deg no OS.a2w2d</t>
+  </si>
+  <si>
+    <t>d 1.5 deg OS.a2w2d</t>
+  </si>
+  <si>
+    <t>c 2 deg (67%).a2w2d</t>
+  </si>
+  <si>
+    <t>b 2 deg (50%).a2w2d</t>
+  </si>
+  <si>
+    <t>a 3 deg.a2w2d</t>
+  </si>
+  <si>
+    <t>kAnn</t>
+  </si>
+  <si>
+    <t>k12</t>
+  </si>
+  <si>
+    <t>j12</t>
+  </si>
+  <si>
+    <t>i24</t>
+  </si>
+  <si>
+    <t>h48</t>
+  </si>
+  <si>
+    <t>g64</t>
+  </si>
+  <si>
+    <t>f97p50</t>
+  </si>
+  <si>
+    <t>f96p10</t>
+  </si>
+  <si>
+    <t>f96p90</t>
   </si>
 </sst>
 </file>
@@ -1394,1057 +1788,2735 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:P40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A01595-4651-4682-AE2C-4C2356B80CEF}">
+  <dimension ref="A1:U60"/>
   <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="1.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H1" t="s">
+    <row r="1" spans="1:21">
+      <c r="I1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
-      <c r="H2" t="s">
-        <v>128</v>
-      </c>
+    <row r="2" spans="1:21">
       <c r="I2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>260</v>
+      </c>
+      <c r="J2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>9</v>
-      </c>
-      <c r="H5" t="str">
-        <f>"sg_"&amp;H2</f>
-        <v>sg_ngfs</v>
       </c>
       <c r="I5" t="str">
         <f>"sg_"&amp;I2</f>
+        <v>sg_ar6_r10</v>
+      </c>
+      <c r="J5" t="str">
+        <f>"sg_"&amp;J2</f>
         <v>sg_timeslice</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="str">
-        <f>$A$1&amp;TEXT(N6,"0000")</f>
-        <v>vstacks_t1~0001</v>
+    <row r="6" spans="1:21">
+      <c r="A6">
+        <v>1</v>
       </c>
       <c r="B6" t="str">
-        <f>G6</f>
-        <v>Postponed Transition_3d</v>
-      </c>
-      <c r="G6" t="str">
-        <f>H6&amp;P6</f>
-        <v>Postponed Transition_3d</v>
-      </c>
-      <c r="H6" t="s">
+        <f t="shared" ref="B6:B60" si="0">"vstacks_"&amp;VLOOKUP(A6,$S$6:$T$18,2,FALSE)&amp;"~"&amp;TEXT(O6,"0000")</f>
+        <v>vstacks_s1p1v1_d~0001</v>
+      </c>
+      <c r="C6" t="str">
+        <f>H6</f>
+        <v>e 1.5 deg no OS.e3d</v>
+      </c>
+      <c r="H6" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,I6:J6)</f>
+        <v>e 1.5 deg no OS.e3d</v>
+      </c>
+      <c r="I6" t="s">
+        <v>258</v>
+      </c>
+      <c r="J6" t="str">
+        <f>Q6</f>
+        <v>e3d</v>
+      </c>
+      <c r="L6" t="s">
+        <v>250</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="str">
+        <f>VLOOKUP(A6,$S$6:$U$17,3,FALSE)</f>
+        <v>e3d</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6" t="s">
+        <v>230</v>
+      </c>
+      <c r="U6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1p1v1_d~0002</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" ref="C7:C60" si="1">H7</f>
+        <v>d 1.5 deg OS.e3d</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" ref="H7:H60" si="2">_xlfn.TEXTJOIN(".",TRUE,I7:J7)</f>
+        <v>d 1.5 deg OS.e3d</v>
+      </c>
+      <c r="I7" t="s">
+        <v>257</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" ref="J7:J60" si="3">Q7</f>
+        <v>e3d</v>
+      </c>
+      <c r="L7" t="s">
+        <v>251</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" ref="Q7:Q60" si="4">VLOOKUP(A7,$S$6:$U$17,3,FALSE)</f>
+        <v>e3d</v>
+      </c>
+      <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7" t="s">
+        <v>231</v>
+      </c>
+      <c r="U7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1p1v1_d~0003</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).e3d</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).e3d</v>
+      </c>
+      <c r="I8" t="s">
+        <v>256</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="3"/>
+        <v>e3d</v>
+      </c>
+      <c r="L8" t="s">
+        <v>252</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="4"/>
+        <v>e3d</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8" t="s">
+        <v>232</v>
+      </c>
+      <c r="U8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1p1v1_d~0004</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).e3d</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).e3d</v>
+      </c>
+      <c r="I9" t="s">
+        <v>255</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="3"/>
+        <v>e3d</v>
+      </c>
+      <c r="L9" t="s">
+        <v>253</v>
+      </c>
+      <c r="O9">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="4"/>
+        <v>e3d</v>
+      </c>
+      <c r="S9">
+        <v>4</v>
+      </c>
+      <c r="T9" t="s">
+        <v>233</v>
+      </c>
+      <c r="U9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1p1v1_d~0005</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.e3d</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.e3d</v>
+      </c>
+      <c r="I10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="3"/>
+        <v>e3d</v>
+      </c>
+      <c r="L10" t="s">
         <v>254</v>
       </c>
-      <c r="I6" t="s">
-        <v>132</v>
-      </c>
-      <c r="N6">
+      <c r="O10">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="4"/>
+        <v>e3d</v>
+      </c>
+      <c r="S10">
+        <v>5</v>
+      </c>
+      <c r="T10" t="s">
+        <v>234</v>
+      </c>
+      <c r="U10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11">
+        <f>A6+1</f>
+        <v>2</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s3p3v3_d~0001</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.d9d</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.d9d</v>
+      </c>
+      <c r="I11" t="str">
+        <f>I6</f>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="3"/>
+        <v>d9d</v>
+      </c>
+      <c r="O11">
+        <f>O6</f>
         <v>1</v>
       </c>
-      <c r="P6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="str">
-        <f t="shared" ref="A7:A12" si="0">$A$1&amp;TEXT(N7,"0000")</f>
-        <v>vstacks_t1~0002</v>
-      </c>
-      <c r="B7" t="str">
-        <f t="shared" ref="B7:B26" si="1">G7</f>
-        <v>Target Net Zero 2050_3d</v>
-      </c>
-      <c r="G7" t="str">
-        <f t="shared" ref="G7:G26" si="2">H7&amp;P7</f>
-        <v>Target Net Zero 2050_3d</v>
-      </c>
-      <c r="H7" t="s">
-        <v>255</v>
-      </c>
-      <c r="I7" t="s">
-        <v>132</v>
-      </c>
-      <c r="N7">
+      <c r="Q11" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="S11">
+        <v>6</v>
+      </c>
+      <c r="T11" t="s">
+        <v>235</v>
+      </c>
+      <c r="U11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12">
+        <f t="shared" ref="A12:A60" si="5">A7+1</f>
         <v>2</v>
       </c>
-      <c r="P7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="str">
-        <f t="shared" si="0"/>
-        <v>vstacks_t1~0003</v>
-      </c>
-      <c r="B8" t="str">
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s3p3v3_d~0002</v>
+      </c>
+      <c r="C12" t="str">
         <f t="shared" si="1"/>
-        <v>Declared NDCs_3d</v>
-      </c>
-      <c r="G8" t="str">
-        <f t="shared" si="2"/>
-        <v>Declared NDCs_3d</v>
-      </c>
-      <c r="H8" t="s">
-        <v>252</v>
-      </c>
-      <c r="I8" t="s">
-        <v>132</v>
-      </c>
-      <c r="N8">
+        <v>d 1.5 deg OS.d9d</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.d9d</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" ref="I12:I60" si="6">I7</f>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="3"/>
+        <v>d9d</v>
+      </c>
+      <c r="O12">
+        <f t="shared" ref="O12:O60" si="7">O7</f>
+        <v>2</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="S12">
+        <v>7</v>
+      </c>
+      <c r="T12" t="s">
+        <v>236</v>
+      </c>
+      <c r="U12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s3p3v3_d~0003</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).d9d</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).d9d</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="3"/>
+        <v>d9d</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="P8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="str">
-        <f t="shared" si="0"/>
-        <v>vstacks_t1~0004</v>
-      </c>
-      <c r="B9" t="str">
+      <c r="Q13" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="S13">
+        <v>8</v>
+      </c>
+      <c r="T13" t="s">
+        <v>237</v>
+      </c>
+      <c r="U13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s3p3v3_d~0004</v>
+      </c>
+      <c r="C14" t="str">
         <f t="shared" si="1"/>
-        <v>Limited to 2 deg_3d</v>
-      </c>
-      <c r="G9" t="str">
-        <f t="shared" si="2"/>
-        <v>Limited to 2 deg_3d</v>
-      </c>
-      <c r="H9" t="s">
-        <v>253</v>
-      </c>
-      <c r="I9" t="s">
-        <v>132</v>
-      </c>
-      <c r="N9">
+        <v>b 2 deg (50%).d9d</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).d9d</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="3"/>
+        <v>d9d</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="P9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" t="str">
-        <f t="shared" si="0"/>
-        <v>vstacks_t1~0005</v>
-      </c>
-      <c r="B10" t="str">
+      <c r="Q14" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="S14">
+        <v>9</v>
+      </c>
+      <c r="T14" t="s">
+        <v>239</v>
+      </c>
+      <c r="U14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s3p3v3_d~0005</v>
+      </c>
+      <c r="C15" t="str">
         <f t="shared" si="1"/>
-        <v>Current Policies_3d</v>
-      </c>
-      <c r="G10" t="str">
-        <f t="shared" si="2"/>
-        <v>Current Policies_3d</v>
-      </c>
-      <c r="H10" t="s">
-        <v>256</v>
-      </c>
-      <c r="I10" t="s">
-        <v>132</v>
-      </c>
-      <c r="N10">
-        <v>5</v>
-      </c>
-      <c r="P10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" t="str">
-        <f t="shared" si="0"/>
-        <v>vstacks_t1~0006</v>
-      </c>
-      <c r="B11" t="str">
-        <f t="shared" si="1"/>
-        <v>Low demand_3d</v>
-      </c>
-      <c r="G11" t="str">
-        <f t="shared" si="2"/>
-        <v>Low demand_3d</v>
-      </c>
-      <c r="H11" t="s">
-        <v>130</v>
-      </c>
-      <c r="I11" t="s">
-        <v>132</v>
-      </c>
-      <c r="N11">
-        <v>6</v>
-      </c>
-      <c r="P11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" t="str">
-        <f t="shared" si="0"/>
-        <v>vstacks_t1~0007</v>
-      </c>
-      <c r="B12" t="str">
-        <f t="shared" si="1"/>
-        <v>Fragmented World_3d</v>
-      </c>
-      <c r="G12" t="str">
-        <f t="shared" si="2"/>
-        <v>Fragmented World_3d</v>
-      </c>
-      <c r="H12" t="s">
-        <v>131</v>
-      </c>
-      <c r="I12" t="s">
-        <v>132</v>
-      </c>
-      <c r="N12">
-        <v>7</v>
-      </c>
-      <c r="P12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" t="str">
-        <f>$B$1&amp;TEXT(N13,"0000")</f>
-        <v>vstacks_t5~0001</v>
-      </c>
-      <c r="B13" t="str">
-        <f t="shared" si="1"/>
-        <v>Postponed Transition_15d</v>
-      </c>
-      <c r="G13" t="str">
-        <f t="shared" si="2"/>
-        <v>Postponed Transition_15d</v>
-      </c>
-      <c r="H13" t="str">
-        <f>H6</f>
-        <v>Postponed Transition</v>
-      </c>
-      <c r="I13" t="s">
-        <v>133</v>
-      </c>
-      <c r="N13">
-        <f>N6</f>
-        <v>1</v>
-      </c>
-      <c r="P13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" t="str">
-        <f t="shared" ref="A14:A19" si="3">$B$1&amp;TEXT(N14,"0000")</f>
-        <v>vstacks_t5~0002</v>
-      </c>
-      <c r="B14" t="str">
-        <f t="shared" si="1"/>
-        <v>Target Net Zero 2050_15d</v>
-      </c>
-      <c r="G14" t="str">
-        <f t="shared" si="2"/>
-        <v>Target Net Zero 2050_15d</v>
-      </c>
-      <c r="H14" t="str">
-        <f t="shared" ref="H14:H40" si="4">H7</f>
-        <v>Target Net Zero 2050</v>
-      </c>
-      <c r="I14" t="s">
-        <v>133</v>
-      </c>
-      <c r="N14">
-        <f t="shared" ref="N14:N40" si="5">N7</f>
-        <v>2</v>
-      </c>
-      <c r="P14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" t="str">
-        <f t="shared" si="3"/>
-        <v>vstacks_t5~0003</v>
-      </c>
-      <c r="B15" t="str">
-        <f t="shared" si="1"/>
-        <v>Declared NDCs_15d</v>
-      </c>
-      <c r="G15" t="str">
-        <f t="shared" si="2"/>
-        <v>Declared NDCs_15d</v>
+        <v>a 3 deg.d9d</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="4"/>
-        <v>Declared NDCs</v>
-      </c>
-      <c r="I15" t="s">
-        <v>133</v>
-      </c>
-      <c r="N15">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.d9d</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="3"/>
+        <v>d9d</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="S15">
+        <v>10</v>
+      </c>
+      <c r="T15" t="s">
+        <v>238</v>
+      </c>
+      <c r="U15" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" t="str">
-        <f t="shared" si="3"/>
-        <v>vstacks_t5~0004</v>
-      </c>
       <c r="B16" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w~0001</v>
+      </c>
+      <c r="C16" t="str">
         <f t="shared" si="1"/>
-        <v>Limited to 2 deg_15d</v>
-      </c>
-      <c r="G16" t="str">
-        <f t="shared" si="2"/>
-        <v>Limited to 2 deg_15d</v>
+        <v>e 1.5 deg no OS.b2w</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="4"/>
-        <v>Limited to 2 deg</v>
-      </c>
-      <c r="I16" t="s">
-        <v>133</v>
-      </c>
-      <c r="N16">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.b2w</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="3"/>
+        <v>b2w</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q16" t="str">
+        <f t="shared" si="4"/>
+        <v>b2w</v>
+      </c>
+      <c r="S16">
+        <v>11</v>
+      </c>
+      <c r="T16" t="s">
+        <v>263</v>
+      </c>
+      <c r="U16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="B17" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w~0002</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.b2w</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.b2w</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="3"/>
+        <v>b2w</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="4"/>
+        <v>b2w</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="B18" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w~0003</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).b2w</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).b2w</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="3"/>
+        <v>b2w</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q18" t="str">
+        <f t="shared" si="4"/>
+        <v>b2w</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="B19" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w~0004</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).b2w</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).b2w</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="3"/>
+        <v>b2w</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q19" t="str">
+        <f t="shared" si="4"/>
+        <v>b2w</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="B20" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w~0005</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.b2w</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.b2w</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="3"/>
+        <v>b2w</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q20" t="str">
+        <f t="shared" si="4"/>
+        <v>b2w</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="P16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" t="str">
-        <f t="shared" si="3"/>
-        <v>vstacks_t5~0005</v>
-      </c>
-      <c r="B17" t="str">
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w_p2_d~0001</v>
+      </c>
+      <c r="C21" t="str">
         <f t="shared" si="1"/>
-        <v>Current Policies_15d</v>
-      </c>
-      <c r="G17" t="str">
-        <f t="shared" si="2"/>
-        <v>Current Policies_15d</v>
-      </c>
-      <c r="H17" t="str">
-        <f t="shared" si="4"/>
-        <v>Current Policies</v>
-      </c>
-      <c r="I17" t="s">
-        <v>133</v>
-      </c>
-      <c r="N17">
+        <v>e 1.5 deg no OS.a2w2d</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.a2w2d</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="3"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q21" t="str">
+        <f t="shared" si="4"/>
+        <v>a2w2d</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="P17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" t="str">
-        <f t="shared" si="3"/>
-        <v>vstacks_t5~0006</v>
-      </c>
-      <c r="B18" t="str">
+        <v>4</v>
+      </c>
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w_p2_d~0002</v>
+      </c>
+      <c r="C22" t="str">
         <f t="shared" si="1"/>
-        <v>Low demand_15d</v>
-      </c>
-      <c r="G18" t="str">
-        <f t="shared" si="2"/>
-        <v>Low demand_15d</v>
-      </c>
-      <c r="H18" t="str">
-        <f t="shared" si="4"/>
-        <v>Low demand</v>
-      </c>
-      <c r="I18" t="s">
-        <v>133</v>
-      </c>
-      <c r="N18">
+        <v>d 1.5 deg OS.a2w2d</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.a2w2d</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="3"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q22" t="str">
+        <f t="shared" si="4"/>
+        <v>a2w2d</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w_p2_d~0003</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).a2w2d</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).a2w2d</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="3"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q23" t="str">
+        <f t="shared" si="4"/>
+        <v>a2w2d</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w_p2_d~0004</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).a2w2d</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).a2w2d</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="3"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q24" t="str">
+        <f t="shared" si="4"/>
+        <v>a2w2d</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s2_w_p2_d~0005</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.a2w2d</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.a2w2d</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="3"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q25" t="str">
+        <f t="shared" si="4"/>
+        <v>a2w2d</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts12_clu~0001</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.hTS12c</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.hTS12c</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="3"/>
+        <v>hTS12c</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q26" t="str">
+        <f t="shared" si="4"/>
+        <v>hTS12c</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts12_clu~0002</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.hTS12c</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.hTS12c</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="3"/>
+        <v>hTS12c</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q27" t="str">
+        <f t="shared" si="4"/>
+        <v>hTS12c</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts12_clu~0003</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).hTS12c</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).hTS12c</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="3"/>
+        <v>hTS12c</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q28" t="str">
+        <f t="shared" si="4"/>
+        <v>hTS12c</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts12_clu~0004</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).hTS12c</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).hTS12c</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="3"/>
+        <v>hTS12c</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q29" t="str">
+        <f t="shared" si="4"/>
+        <v>hTS12c</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts12_clu~0005</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.hTS12c</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.hTS12c</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="3"/>
+        <v>hTS12c</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q30" t="str">
+        <f t="shared" si="4"/>
+        <v>hTS12c</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="P18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" t="str">
-        <f t="shared" si="3"/>
-        <v>vstacks_t5~0007</v>
-      </c>
-      <c r="B19" t="str">
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts24_clu~0001</v>
+      </c>
+      <c r="C31" t="str">
         <f t="shared" si="1"/>
-        <v>Fragmented World_15d</v>
-      </c>
-      <c r="G19" t="str">
-        <f t="shared" si="2"/>
-        <v>Fragmented World_15d</v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="4"/>
-        <v>Fragmented World</v>
-      </c>
-      <c r="I19" t="s">
-        <v>133</v>
-      </c>
-      <c r="N19">
+        <v>e 1.5 deg no OS.gTS24c</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.gTS24c</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="3"/>
+        <v>gTS24c</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q31" t="str">
+        <f t="shared" si="4"/>
+        <v>gTS24c</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts24_clu~0002</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.gTS24c</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.gTS24c</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" si="3"/>
+        <v>gTS24c</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q32" t="str">
+        <f t="shared" si="4"/>
+        <v>gTS24c</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts24_clu~0003</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).gTS24c</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).gTS24c</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="3"/>
+        <v>gTS24c</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q33" t="str">
+        <f t="shared" si="4"/>
+        <v>gTS24c</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts24_clu~0004</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).gTS24c</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).gTS24c</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="3"/>
+        <v>gTS24c</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q34" t="str">
+        <f t="shared" si="4"/>
+        <v>gTS24c</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts24_clu~0005</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.gTS24c</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.gTS24c</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="3"/>
+        <v>gTS24c</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q35" t="str">
+        <f t="shared" si="4"/>
+        <v>gTS24c</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="P19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" t="str">
-        <f>$C$1&amp;TEXT(N20,"0000")</f>
-        <v>vstacks_w2~0001</v>
-      </c>
-      <c r="B20" t="str">
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts48_clu~0001</v>
+      </c>
+      <c r="C36" t="str">
         <f t="shared" si="1"/>
-        <v>Postponed Transition_2w</v>
-      </c>
-      <c r="G20" t="str">
-        <f t="shared" si="2"/>
-        <v>Postponed Transition_2w</v>
-      </c>
-      <c r="H20" t="str">
-        <f t="shared" si="4"/>
-        <v>Postponed Transition</v>
-      </c>
-      <c r="I20" t="s">
-        <v>134</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="5"/>
+        <v>e 1.5 deg no OS.fTS48c</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.fTS48c</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="3"/>
+        <v>fTS48c</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="P20" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" t="str">
-        <f t="shared" ref="A21:A26" si="6">$C$1&amp;TEXT(N21,"0000")</f>
-        <v>vstacks_w2~0002</v>
-      </c>
-      <c r="B21" t="str">
-        <f t="shared" si="1"/>
-        <v>Target Net Zero 2050_2w</v>
-      </c>
-      <c r="G21" t="str">
-        <f t="shared" si="2"/>
-        <v>Target Net Zero 2050_2w</v>
-      </c>
-      <c r="H21" t="str">
-        <f t="shared" si="4"/>
-        <v>Target Net Zero 2050</v>
-      </c>
-      <c r="I21" t="s">
-        <v>134</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="P21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" t="str">
-        <f t="shared" si="6"/>
-        <v>vstacks_w2~0003</v>
-      </c>
-      <c r="B22" t="str">
-        <f t="shared" si="1"/>
-        <v>Declared NDCs_2w</v>
-      </c>
-      <c r="G22" t="str">
-        <f t="shared" si="2"/>
-        <v>Declared NDCs_2w</v>
-      </c>
-      <c r="H22" t="str">
-        <f t="shared" si="4"/>
-        <v>Declared NDCs</v>
-      </c>
-      <c r="I22" t="s">
-        <v>134</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="P22" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" t="str">
-        <f t="shared" si="6"/>
-        <v>vstacks_w2~0004</v>
-      </c>
-      <c r="B23" t="str">
-        <f t="shared" si="1"/>
-        <v>Limited to 2 deg_2w</v>
-      </c>
-      <c r="G23" t="str">
-        <f t="shared" si="2"/>
-        <v>Limited to 2 deg_2w</v>
-      </c>
-      <c r="H23" t="str">
-        <f t="shared" si="4"/>
-        <v>Limited to 2 deg</v>
-      </c>
-      <c r="I23" t="s">
-        <v>134</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="P23" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" t="str">
-        <f t="shared" si="6"/>
-        <v>vstacks_w2~0005</v>
-      </c>
-      <c r="B24" t="str">
-        <f t="shared" si="1"/>
-        <v>Current Policies_2w</v>
-      </c>
-      <c r="G24" t="str">
-        <f t="shared" si="2"/>
-        <v>Current Policies_2w</v>
-      </c>
-      <c r="H24" t="str">
-        <f t="shared" si="4"/>
-        <v>Current Policies</v>
-      </c>
-      <c r="I24" t="s">
-        <v>134</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="P24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" t="str">
-        <f t="shared" si="6"/>
-        <v>vstacks_w2~0006</v>
-      </c>
-      <c r="B25" t="str">
-        <f t="shared" si="1"/>
-        <v>Low demand_2w</v>
-      </c>
-      <c r="G25" t="str">
-        <f t="shared" si="2"/>
-        <v>Low demand_2w</v>
-      </c>
-      <c r="H25" t="str">
-        <f t="shared" si="4"/>
-        <v>Low demand</v>
-      </c>
-      <c r="I25" t="s">
-        <v>134</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="P25" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" t="str">
-        <f t="shared" si="6"/>
-        <v>vstacks_w2~0007</v>
-      </c>
-      <c r="B26" t="str">
-        <f t="shared" si="1"/>
-        <v>Fragmented World_2w</v>
-      </c>
-      <c r="G26" t="str">
-        <f t="shared" si="2"/>
-        <v>Fragmented World_2w</v>
-      </c>
-      <c r="H26" t="str">
-        <f t="shared" si="4"/>
-        <v>Fragmented World</v>
-      </c>
-      <c r="I26" t="s">
-        <v>134</v>
-      </c>
-      <c r="N26">
+      <c r="Q36" t="str">
+        <f t="shared" si="4"/>
+        <v>fTS48c</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="P26" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" t="str">
-        <f>$D$1&amp;TEXT(N27,"0000")</f>
-        <v>vstacks_ts16~0001</v>
-      </c>
-      <c r="B27" t="str">
-        <f t="shared" ref="B27:B40" si="7">G27</f>
-        <v>Postponed Transition_16</v>
-      </c>
-      <c r="G27" t="str">
-        <f t="shared" ref="G27:G40" si="8">H27&amp;P27</f>
-        <v>Postponed Transition_16</v>
-      </c>
-      <c r="H27" t="str">
-        <f t="shared" si="4"/>
-        <v>Postponed Transition</v>
-      </c>
-      <c r="I27" t="s">
-        <v>173</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="P27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" t="str">
-        <f t="shared" ref="A28:A33" si="9">$D$1&amp;TEXT(N28,"0000")</f>
-        <v>vstacks_ts16~0002</v>
-      </c>
-      <c r="B28" t="str">
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts48_clu~0002</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.fTS48c</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.fTS48c</v>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="3"/>
+        <v>fTS48c</v>
+      </c>
+      <c r="O37">
         <f t="shared" si="7"/>
-        <v>Target Net Zero 2050_16</v>
-      </c>
-      <c r="G28" t="str">
-        <f t="shared" si="8"/>
-        <v>Target Net Zero 2050_16</v>
-      </c>
-      <c r="H28" t="str">
-        <f t="shared" si="4"/>
-        <v>Target Net Zero 2050</v>
-      </c>
-      <c r="I28" t="s">
-        <v>173</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="P28" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="A29" t="str">
-        <f t="shared" si="9"/>
-        <v>vstacks_ts16~0003</v>
-      </c>
-      <c r="B29" t="str">
-        <f t="shared" si="7"/>
-        <v>Declared NDCs_16</v>
-      </c>
-      <c r="G29" t="str">
-        <f t="shared" si="8"/>
-        <v>Declared NDCs_16</v>
-      </c>
-      <c r="H29" t="str">
-        <f t="shared" si="4"/>
-        <v>Declared NDCs</v>
-      </c>
-      <c r="I29" t="s">
-        <v>173</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="P29" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" t="str">
-        <f t="shared" si="9"/>
-        <v>vstacks_ts16~0004</v>
-      </c>
-      <c r="B30" t="str">
-        <f t="shared" si="7"/>
-        <v>Limited to 2 deg_16</v>
-      </c>
-      <c r="G30" t="str">
-        <f t="shared" si="8"/>
-        <v>Limited to 2 deg_16</v>
-      </c>
-      <c r="H30" t="str">
-        <f t="shared" si="4"/>
-        <v>Limited to 2 deg</v>
-      </c>
-      <c r="I30" t="s">
-        <v>173</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="P30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" t="str">
-        <f t="shared" si="9"/>
-        <v>vstacks_ts16~0005</v>
-      </c>
-      <c r="B31" t="str">
-        <f t="shared" si="7"/>
-        <v>Current Policies_16</v>
-      </c>
-      <c r="G31" t="str">
-        <f t="shared" si="8"/>
-        <v>Current Policies_16</v>
-      </c>
-      <c r="H31" t="str">
-        <f t="shared" si="4"/>
-        <v>Current Policies</v>
-      </c>
-      <c r="I31" t="s">
-        <v>173</v>
-      </c>
-      <c r="N31">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="P31" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32" t="str">
-        <f t="shared" si="9"/>
-        <v>vstacks_ts16~0006</v>
-      </c>
-      <c r="B32" t="str">
-        <f t="shared" si="7"/>
-        <v>Low demand_16</v>
-      </c>
-      <c r="G32" t="str">
-        <f t="shared" si="8"/>
-        <v>Low demand_16</v>
-      </c>
-      <c r="H32" t="str">
-        <f t="shared" si="4"/>
-        <v>Low demand</v>
-      </c>
-      <c r="I32" t="s">
-        <v>173</v>
-      </c>
-      <c r="N32">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="P32" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" t="str">
-        <f t="shared" si="9"/>
-        <v>vstacks_ts16~0007</v>
-      </c>
-      <c r="B33" t="str">
-        <f t="shared" si="7"/>
-        <v>Fragmented World_16</v>
-      </c>
-      <c r="G33" t="str">
-        <f t="shared" si="8"/>
-        <v>Fragmented World_16</v>
-      </c>
-      <c r="H33" t="str">
-        <f t="shared" si="4"/>
-        <v>Fragmented World</v>
-      </c>
-      <c r="I33" t="s">
-        <v>173</v>
-      </c>
-      <c r="N33">
+      <c r="Q37" t="str">
+        <f t="shared" si="4"/>
+        <v>fTS48c</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="P33" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" t="str">
-        <f>$E$1&amp;TEXT(N34,"0000")</f>
-        <v>vstacks_t_annual~0001</v>
-      </c>
-      <c r="B34" t="str">
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts48_clu~0003</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).fTS48c</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).fTS48c</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="3"/>
+        <v>fTS48c</v>
+      </c>
+      <c r="O38">
         <f t="shared" si="7"/>
-        <v>Postponed Transition_ann</v>
-      </c>
-      <c r="G34" t="str">
-        <f t="shared" si="8"/>
-        <v>Postponed Transition_ann</v>
-      </c>
-      <c r="H34" t="str">
-        <f t="shared" si="4"/>
-        <v>Postponed Transition</v>
-      </c>
-      <c r="I34" t="s">
-        <v>174</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="P34" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" t="str">
-        <f t="shared" ref="A35:A40" si="10">$E$1&amp;TEXT(N35,"0000")</f>
-        <v>vstacks_t_annual~0002</v>
-      </c>
-      <c r="B35" t="str">
-        <f t="shared" si="7"/>
-        <v>Target Net Zero 2050_ann</v>
-      </c>
-      <c r="G35" t="str">
-        <f t="shared" si="8"/>
-        <v>Target Net Zero 2050_ann</v>
-      </c>
-      <c r="H35" t="str">
-        <f t="shared" si="4"/>
-        <v>Target Net Zero 2050</v>
-      </c>
-      <c r="I35" t="s">
-        <v>174</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="P35" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" t="str">
-        <f t="shared" si="10"/>
-        <v>vstacks_t_annual~0003</v>
-      </c>
-      <c r="B36" t="str">
-        <f t="shared" si="7"/>
-        <v>Declared NDCs_ann</v>
-      </c>
-      <c r="G36" t="str">
-        <f t="shared" si="8"/>
-        <v>Declared NDCs_ann</v>
-      </c>
-      <c r="H36" t="str">
-        <f t="shared" si="4"/>
-        <v>Declared NDCs</v>
-      </c>
-      <c r="I36" t="s">
-        <v>174</v>
-      </c>
-      <c r="N36">
-        <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P36" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" t="str">
-        <f t="shared" si="10"/>
-        <v>vstacks_t_annual~0004</v>
-      </c>
-      <c r="B37" t="str">
-        <f t="shared" si="7"/>
-        <v>Limited to 2 deg_ann</v>
-      </c>
-      <c r="G37" t="str">
-        <f t="shared" si="8"/>
-        <v>Limited to 2 deg_ann</v>
-      </c>
-      <c r="H37" t="str">
-        <f t="shared" si="4"/>
-        <v>Limited to 2 deg</v>
-      </c>
-      <c r="I37" t="s">
-        <v>174</v>
-      </c>
-      <c r="N37">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="P37" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" t="str">
-        <f t="shared" si="10"/>
-        <v>vstacks_t_annual~0005</v>
-      </c>
-      <c r="B38" t="str">
-        <f t="shared" si="7"/>
-        <v>Current Policies_ann</v>
-      </c>
-      <c r="G38" t="str">
-        <f t="shared" si="8"/>
-        <v>Current Policies_ann</v>
-      </c>
-      <c r="H38" t="str">
-        <f t="shared" si="4"/>
-        <v>Current Policies</v>
-      </c>
-      <c r="I38" t="s">
-        <v>174</v>
-      </c>
-      <c r="N38">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="P38" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="A39" t="str">
-        <f t="shared" si="10"/>
-        <v>vstacks_t_annual~0006</v>
-      </c>
-      <c r="B39" t="str">
-        <f t="shared" si="7"/>
-        <v>Low demand_ann</v>
-      </c>
-      <c r="G39" t="str">
-        <f t="shared" si="8"/>
-        <v>Low demand_ann</v>
-      </c>
-      <c r="H39" t="str">
-        <f t="shared" si="4"/>
-        <v>Low demand</v>
-      </c>
-      <c r="I39" t="s">
-        <v>174</v>
-      </c>
-      <c r="N39">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="P39" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="A40" t="str">
-        <f t="shared" si="10"/>
-        <v>vstacks_t_annual~0007</v>
-      </c>
-      <c r="B40" t="str">
-        <f t="shared" si="7"/>
-        <v>Fragmented World_ann</v>
-      </c>
-      <c r="G40" t="str">
-        <f t="shared" si="8"/>
-        <v>Fragmented World_ann</v>
-      </c>
-      <c r="H40" t="str">
-        <f t="shared" si="4"/>
-        <v>Fragmented World</v>
-      </c>
-      <c r="I40" t="s">
-        <v>174</v>
-      </c>
-      <c r="N40">
+      <c r="Q38" t="str">
+        <f t="shared" si="4"/>
+        <v>fTS48c</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="P40" t="s">
-        <v>176</v>
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts48_clu~0004</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).fTS48c</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).fTS48c</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="3"/>
+        <v>fTS48c</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q39" t="str">
+        <f t="shared" si="4"/>
+        <v>fTS48c</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts48_clu~0005</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.fTS48c</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.fTS48c</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="3"/>
+        <v>fTS48c</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q40" t="str">
+        <f t="shared" si="4"/>
+        <v>fTS48c</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s5p5v5_d~0001</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.c15d</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.c15d</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="3"/>
+        <v>c15d</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q41" t="str">
+        <f t="shared" si="4"/>
+        <v>c15d</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s5p5v5_d~0002</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.c15d</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.c15d</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="3"/>
+        <v>c15d</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q42" t="str">
+        <f t="shared" si="4"/>
+        <v>c15d</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="B43" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s5p5v5_d~0003</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).c15d</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).c15d</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="3"/>
+        <v>c15d</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q43" t="str">
+        <f t="shared" si="4"/>
+        <v>c15d</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="B44" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s5p5v5_d~0004</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).c15d</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).c15d</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="3"/>
+        <v>c15d</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q44" t="str">
+        <f t="shared" si="4"/>
+        <v>c15d</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="B45" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s5p5v5_d~0005</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.c15d</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.c15d</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="3"/>
+        <v>c15d</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q45" t="str">
+        <f t="shared" si="4"/>
+        <v>c15d</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="B46" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_12~0001</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.iTS12</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.iTS12</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="3"/>
+        <v>iTS12</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q46" t="str">
+        <f t="shared" si="4"/>
+        <v>iTS12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="B47" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_12~0002</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.iTS12</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.iTS12</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="3"/>
+        <v>iTS12</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q47" t="str">
+        <f t="shared" si="4"/>
+        <v>iTS12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="B48" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_12~0003</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).iTS12</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).iTS12</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="3"/>
+        <v>iTS12</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q48" t="str">
+        <f t="shared" si="4"/>
+        <v>iTS12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="B49" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_12~0004</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).iTS12</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).iTS12</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="3"/>
+        <v>iTS12</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q49" t="str">
+        <f t="shared" si="4"/>
+        <v>iTS12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="A50">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="B50" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_12~0005</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.iTS12</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.iTS12</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="3"/>
+        <v>iTS12</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q50" t="str">
+        <f t="shared" si="4"/>
+        <v>iTS12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="B51" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_annual~0001</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.jAnn</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.jAnn</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="3"/>
+        <v>jAnn</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q51" t="str">
+        <f t="shared" si="4"/>
+        <v>jAnn</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="B52" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_annual~0002</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.jAnn</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.jAnn</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="3"/>
+        <v>jAnn</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q52" t="str">
+        <f t="shared" si="4"/>
+        <v>jAnn</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="B53" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_annual~0003</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).jAnn</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).jAnn</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="3"/>
+        <v>jAnn</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q53" t="str">
+        <f t="shared" si="4"/>
+        <v>jAnn</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_annual~0004</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).jAnn</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).jAnn</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="3"/>
+        <v>jAnn</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q54" t="str">
+        <f t="shared" si="4"/>
+        <v>jAnn</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_ts_annual~0005</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.jAnn</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.jAnn</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="3"/>
+        <v>jAnn</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q55" t="str">
+        <f t="shared" si="4"/>
+        <v>jAnn</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1_d~0001</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.f3d</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.f3d</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="3"/>
+        <v>f3d</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q56" t="str">
+        <f t="shared" si="4"/>
+        <v>f3d</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1_d~0002</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.f3d</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.f3d</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="3"/>
+        <v>f3d</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q57" t="str">
+        <f t="shared" si="4"/>
+        <v>f3d</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="B58" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1_d~0003</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).f3d</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).f3d</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="3"/>
+        <v>f3d</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q58" t="str">
+        <f t="shared" si="4"/>
+        <v>f3d</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
+      <c r="A59">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1_d~0004</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).f3d</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).f3d</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="3"/>
+        <v>f3d</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q59" t="str">
+        <f t="shared" si="4"/>
+        <v>f3d</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17">
+      <c r="A60">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="B60" t="str">
+        <f t="shared" si="0"/>
+        <v>vstacks_s1_d~0005</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.f3d</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.f3d</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="3"/>
+        <v>f3d</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q60" t="str">
+        <f t="shared" si="4"/>
+        <v>f3d</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.25" thickBot="1">
+      <c r="A1" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickTop="1" thickBot="1">
+      <c r="A2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="str">
+        <f>D5</f>
+        <v>CCGT</v>
+      </c>
+      <c r="D5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" ref="C6:C49" si="0">D6</f>
+        <v>Int Comb</v>
+      </c>
+      <c r="D6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>Gas_Oil Steam</v>
+      </c>
+      <c r="D7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>OCGT (Peaker)</v>
+      </c>
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>Subcritical Coal</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>Supercritical Coal</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>IGCC</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>Bio Power</v>
+      </c>
+      <c r="D12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>Solar Util</v>
+      </c>
+      <c r="D13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>Wind onshore</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>Wind offshore</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>Geothermal P</v>
+      </c>
+      <c r="D16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydro Dam</v>
+      </c>
+      <c r="D17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydro RoR</v>
+      </c>
+      <c r="D18" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>Nuclear P</v>
+      </c>
+      <c r="D19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>Nuclear SMR</v>
+      </c>
+      <c r="D20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydro pumped stg</v>
+      </c>
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>Util Batt Stg</v>
+      </c>
+      <c r="D22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>EV Batt</v>
+      </c>
+      <c r="D23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>Demand</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>Transformers Dn</v>
+      </c>
+      <c r="D25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>Transformers Up</v>
+      </c>
+      <c r="D26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-220V</v>
+      </c>
+      <c r="D27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-400V</v>
+      </c>
+      <c r="D28" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-380V</v>
+      </c>
+      <c r="D29" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-225V</v>
+      </c>
+      <c r="D30" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-330V</v>
+      </c>
+      <c r="D31" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-275V</v>
+      </c>
+      <c r="D32" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-420V</v>
+      </c>
+      <c r="D33" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-300V</v>
+      </c>
+      <c r="D34" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-500V</v>
+      </c>
+      <c r="D35" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-750V</v>
+      </c>
+      <c r="D36" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-450V</v>
+      </c>
+      <c r="D37" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-515V</v>
+      </c>
+      <c r="D38" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-525V</v>
+      </c>
+      <c r="D39" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-320V</v>
+      </c>
+      <c r="D40" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-150V</v>
+      </c>
+      <c r="D41" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-270V</v>
+      </c>
+      <c r="D42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-350V</v>
+      </c>
+      <c r="D43" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-250V</v>
+      </c>
+      <c r="D44" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-200V</v>
+      </c>
+      <c r="D45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-236V</v>
+      </c>
+      <c r="D46" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v>Grid-600V</v>
+      </c>
+      <c r="D47" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v>Aggregators</v>
+      </c>
+      <c r="D48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v>DUMMY_IMP</v>
+      </c>
+      <c r="D49" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" t="s">
+        <v>262</v>
+      </c>
+      <c r="C50" t="s">
+        <v>132</v>
+      </c>
+      <c r="E50" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>262</v>
+      </c>
+      <c r="C51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" t="s">
+        <v>134</v>
+      </c>
+      <c r="E52" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" t="s">
+        <v>135</v>
+      </c>
+      <c r="E53" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3245E1-8745-41DD-8AE6-2F4FA19D9F1C}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
@@ -2461,33 +4533,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
       <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>75</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>78</v>
-      </c>
-      <c r="G2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H2" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2495,7 +4567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G3"/>
@@ -2540,7 +4612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:D7"/>
@@ -2578,10 +4650,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
         <v>86</v>
-      </c>
-      <c r="B3" t="s">
-        <v>87</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -2593,13 +4665,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4">
         <f>1/8.76*100</f>
@@ -2608,13 +4680,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D5">
         <v>1E-3</v>
@@ -2622,13 +4694,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D6">
         <v>-1E-3</v>
@@ -2636,13 +4708,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="D7">
         <v>-1000</v>
@@ -2654,9 +4726,2829 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet11"/>
+  <dimension ref="B1:X75"/>
+  <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.06640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.33203125" customWidth="1"/>
+    <col min="23" max="23" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.06640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:24">
+      <c r="I1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="2:24">
+      <c r="I2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24">
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24">
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" t="str">
+        <f>"sg_"&amp;I2</f>
+        <v>sg_ar6_r10</v>
+      </c>
+      <c r="J5" t="str">
+        <f>"sg_"&amp;J2</f>
+        <v>sg_timeslice</v>
+      </c>
+      <c r="N5" t="s">
+        <v>297</v>
+      </c>
+      <c r="O5" t="s">
+        <v>298</v>
+      </c>
+      <c r="P5" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>124</v>
+      </c>
+      <c r="R5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24">
+      <c r="B6" t="str">
+        <f>"vs~"&amp;TEXT(P6,"0000")</f>
+        <v>vs~0001</v>
+      </c>
+      <c r="C6" t="str">
+        <f>H6</f>
+        <v>e 1.5 deg no OS.kAnn</v>
+      </c>
+      <c r="H6" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,I6:J6)</f>
+        <v>e 1.5 deg no OS.kAnn</v>
+      </c>
+      <c r="I6" t="str">
+        <f>VLOOKUP(R6,$W$6:$X$12,2,FALSE)</f>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J6" t="str">
+        <f>VLOOKUP(Q6,$T$6:$U$20,2,FALSE)</f>
+        <v>kAnn</v>
+      </c>
+      <c r="L6" t="s">
+        <v>250</v>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6" t="s">
+        <v>301</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>238</v>
+      </c>
+      <c r="R6" t="s">
+        <v>285</v>
+      </c>
+      <c r="T6" t="s">
+        <v>238</v>
+      </c>
+      <c r="U6" t="s">
+        <v>379</v>
+      </c>
+      <c r="W6" t="s">
+        <v>285</v>
+      </c>
+      <c r="X6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24">
+      <c r="B7" t="str">
+        <f t="shared" ref="B7:B60" si="0">"vs~"&amp;TEXT(P7,"0000")</f>
+        <v>vs~0002</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" ref="C7:C26" si="1">H7</f>
+        <v>d 1.5 deg OS.kAnn</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" ref="H7:H60" si="2">_xlfn.TEXTJOIN(".",TRUE,I7:J7)</f>
+        <v>d 1.5 deg OS.kAnn</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" ref="I7:I60" si="3">VLOOKUP(R7,$W$6:$X$12,2,FALSE)</f>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" ref="J7:J60" si="4">VLOOKUP(Q7,$T$6:$U$20,2,FALSE)</f>
+        <v>kAnn</v>
+      </c>
+      <c r="L7" t="s">
+        <v>251</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7" t="s">
+        <v>302</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>238</v>
+      </c>
+      <c r="R7" t="s">
+        <v>286</v>
+      </c>
+      <c r="T7" t="s">
+        <v>307</v>
+      </c>
+      <c r="U7" t="s">
+        <v>380</v>
+      </c>
+      <c r="W7" t="s">
+        <v>286</v>
+      </c>
+      <c r="X7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24">
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0003</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).kAnn</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).kAnn</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="4"/>
+        <v>kAnn</v>
+      </c>
+      <c r="L8" t="s">
+        <v>252</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8" t="s">
+        <v>303</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>238</v>
+      </c>
+      <c r="R8" t="s">
+        <v>287</v>
+      </c>
+      <c r="T8" t="s">
+        <v>313</v>
+      </c>
+      <c r="U8" t="s">
+        <v>381</v>
+      </c>
+      <c r="W8" t="s">
+        <v>287</v>
+      </c>
+      <c r="X8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24">
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0004</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).kAnn</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).kAnn</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="4"/>
+        <v>kAnn</v>
+      </c>
+      <c r="L9" t="s">
+        <v>253</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9" t="s">
+        <v>304</v>
+      </c>
+      <c r="P9">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>238</v>
+      </c>
+      <c r="R9" t="s">
+        <v>288</v>
+      </c>
+      <c r="T9" t="s">
+        <v>319</v>
+      </c>
+      <c r="U9" t="s">
+        <v>382</v>
+      </c>
+      <c r="W9" t="s">
+        <v>288</v>
+      </c>
+      <c r="X9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24">
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0005</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.kAnn</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.kAnn</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="4"/>
+        <v>kAnn</v>
+      </c>
+      <c r="L10" t="s">
+        <v>254</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10" t="s">
+        <v>305</v>
+      </c>
+      <c r="P10">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>238</v>
+      </c>
+      <c r="R10" t="s">
+        <v>289</v>
+      </c>
+      <c r="T10" t="s">
+        <v>325</v>
+      </c>
+      <c r="U10" t="s">
+        <v>383</v>
+      </c>
+      <c r="W10" t="s">
+        <v>289</v>
+      </c>
+      <c r="X10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24">
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0006</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.k12</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.k12</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="4"/>
+        <v>k12</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11" t="s">
+        <v>306</v>
+      </c>
+      <c r="P11">
+        <v>6</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>307</v>
+      </c>
+      <c r="R11" t="s">
+        <v>285</v>
+      </c>
+      <c r="T11" t="s">
+        <v>331</v>
+      </c>
+      <c r="U11" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24">
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0007</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.k12</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.k12</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="4"/>
+        <v>k12</v>
+      </c>
+      <c r="N12">
+        <v>5</v>
+      </c>
+      <c r="O12" t="s">
+        <v>308</v>
+      </c>
+      <c r="P12">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>307</v>
+      </c>
+      <c r="R12" t="s">
+        <v>286</v>
+      </c>
+      <c r="T12" t="s">
+        <v>337</v>
+      </c>
+      <c r="U12" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24">
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0008</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).k12</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).k12</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="4"/>
+        <v>k12</v>
+      </c>
+      <c r="N13">
+        <v>5</v>
+      </c>
+      <c r="O13" t="s">
+        <v>309</v>
+      </c>
+      <c r="P13">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>307</v>
+      </c>
+      <c r="R13" t="s">
+        <v>287</v>
+      </c>
+      <c r="T13" t="s">
+        <v>343</v>
+      </c>
+      <c r="U13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24">
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0009</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).k12</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).k12</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="4"/>
+        <v>k12</v>
+      </c>
+      <c r="N14">
+        <v>5</v>
+      </c>
+      <c r="O14" t="s">
+        <v>310</v>
+      </c>
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>307</v>
+      </c>
+      <c r="R14" t="s">
+        <v>288</v>
+      </c>
+      <c r="T14" t="s">
+        <v>349</v>
+      </c>
+      <c r="U14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24">
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0010</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.k12</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.k12</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="4"/>
+        <v>k12</v>
+      </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15" t="s">
+        <v>311</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>307</v>
+      </c>
+      <c r="R15" t="s">
+        <v>289</v>
+      </c>
+      <c r="T15" t="s">
+        <v>230</v>
+      </c>
+      <c r="U15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="B16" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0011</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.j12</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.j12</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="4"/>
+        <v>j12</v>
+      </c>
+      <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="O16" t="s">
+        <v>312</v>
+      </c>
+      <c r="P16">
+        <v>11</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>313</v>
+      </c>
+      <c r="R16" t="s">
+        <v>285</v>
+      </c>
+      <c r="T16" t="s">
+        <v>231</v>
+      </c>
+      <c r="U16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21">
+      <c r="B17" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0012</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.j12</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.j12</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="4"/>
+        <v>j12</v>
+      </c>
+      <c r="N17">
+        <v>5</v>
+      </c>
+      <c r="O17" t="s">
+        <v>314</v>
+      </c>
+      <c r="P17">
+        <v>12</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>313</v>
+      </c>
+      <c r="R17" t="s">
+        <v>286</v>
+      </c>
+      <c r="T17" t="s">
+        <v>237</v>
+      </c>
+      <c r="U17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21">
+      <c r="B18" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0013</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).j12</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).j12</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="4"/>
+        <v>j12</v>
+      </c>
+      <c r="N18">
+        <v>5</v>
+      </c>
+      <c r="O18" t="s">
+        <v>315</v>
+      </c>
+      <c r="P18">
+        <v>13</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>313</v>
+      </c>
+      <c r="R18" t="s">
+        <v>287</v>
+      </c>
+      <c r="T18" t="s">
+        <v>232</v>
+      </c>
+      <c r="U18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21">
+      <c r="B19" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0014</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).j12</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).j12</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="4"/>
+        <v>j12</v>
+      </c>
+      <c r="N19">
+        <v>5</v>
+      </c>
+      <c r="O19" t="s">
+        <v>316</v>
+      </c>
+      <c r="P19">
+        <v>14</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>313</v>
+      </c>
+      <c r="R19" t="s">
+        <v>288</v>
+      </c>
+      <c r="T19" t="s">
+        <v>233</v>
+      </c>
+      <c r="U19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21">
+      <c r="B20" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0015</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.j12</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.j12</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="4"/>
+        <v>j12</v>
+      </c>
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20" t="s">
+        <v>317</v>
+      </c>
+      <c r="P20">
+        <v>15</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>313</v>
+      </c>
+      <c r="R20" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21">
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0016</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.i24</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.i24</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="4"/>
+        <v>i24</v>
+      </c>
+      <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21" t="s">
+        <v>318</v>
+      </c>
+      <c r="P21">
+        <v>16</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>319</v>
+      </c>
+      <c r="R21" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21">
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0017</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="1"/>
+        <v>d 1.5 deg OS.i24</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.i24</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="4"/>
+        <v>i24</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22" t="s">
+        <v>320</v>
+      </c>
+      <c r="P22">
+        <v>17</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>319</v>
+      </c>
+      <c r="R22" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21">
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0018</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="1"/>
+        <v>c 2 deg (67%).i24</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).i24</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="4"/>
+        <v>i24</v>
+      </c>
+      <c r="N23">
+        <v>5</v>
+      </c>
+      <c r="O23" t="s">
+        <v>321</v>
+      </c>
+      <c r="P23">
+        <v>18</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>319</v>
+      </c>
+      <c r="R23" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21">
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0019</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="1"/>
+        <v>b 2 deg (50%).i24</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).i24</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="4"/>
+        <v>i24</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24" t="s">
+        <v>322</v>
+      </c>
+      <c r="P24">
+        <v>19</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>319</v>
+      </c>
+      <c r="R24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21">
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0020</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="1"/>
+        <v>a 3 deg.i24</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.i24</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="4"/>
+        <v>i24</v>
+      </c>
+      <c r="N25">
+        <v>5</v>
+      </c>
+      <c r="O25" t="s">
+        <v>323</v>
+      </c>
+      <c r="P25">
+        <v>20</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>319</v>
+      </c>
+      <c r="R25" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21">
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0021</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="1"/>
+        <v>e 1.5 deg no OS.h48</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.h48</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="4"/>
+        <v>h48</v>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26" t="s">
+        <v>324</v>
+      </c>
+      <c r="P26">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>325</v>
+      </c>
+      <c r="R26" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21">
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0022</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" ref="C27:C40" si="5">H27</f>
+        <v>d 1.5 deg OS.h48</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.h48</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="4"/>
+        <v>h48</v>
+      </c>
+      <c r="N27">
+        <v>5</v>
+      </c>
+      <c r="O27" t="s">
+        <v>326</v>
+      </c>
+      <c r="P27">
+        <v>22</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>325</v>
+      </c>
+      <c r="R27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21">
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0023</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="5"/>
+        <v>c 2 deg (67%).h48</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).h48</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="4"/>
+        <v>h48</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28" t="s">
+        <v>327</v>
+      </c>
+      <c r="P28">
+        <v>23</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>325</v>
+      </c>
+      <c r="R28" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21">
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0024</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="5"/>
+        <v>b 2 deg (50%).h48</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).h48</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="4"/>
+        <v>h48</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29" t="s">
+        <v>328</v>
+      </c>
+      <c r="P29">
+        <v>24</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>325</v>
+      </c>
+      <c r="R29" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21">
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0025</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="5"/>
+        <v>a 3 deg.h48</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.h48</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="4"/>
+        <v>h48</v>
+      </c>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30" t="s">
+        <v>329</v>
+      </c>
+      <c r="P30">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>325</v>
+      </c>
+      <c r="R30" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21">
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0026</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="5"/>
+        <v>e 1.5 deg no OS.g64</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.g64</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="4"/>
+        <v>g64</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31" t="s">
+        <v>330</v>
+      </c>
+      <c r="P31">
+        <v>26</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>331</v>
+      </c>
+      <c r="R31" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21">
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0027</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="5"/>
+        <v>d 1.5 deg OS.g64</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.g64</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" si="4"/>
+        <v>g64</v>
+      </c>
+      <c r="N32">
+        <v>5</v>
+      </c>
+      <c r="O32" t="s">
+        <v>332</v>
+      </c>
+      <c r="P32">
+        <v>27</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>331</v>
+      </c>
+      <c r="R32" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18">
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0028</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="5"/>
+        <v>c 2 deg (67%).g64</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).g64</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="4"/>
+        <v>g64</v>
+      </c>
+      <c r="N33">
+        <v>5</v>
+      </c>
+      <c r="O33" t="s">
+        <v>333</v>
+      </c>
+      <c r="P33">
+        <v>28</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>331</v>
+      </c>
+      <c r="R33" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18">
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0029</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="5"/>
+        <v>b 2 deg (50%).g64</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).g64</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="4"/>
+        <v>g64</v>
+      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+      <c r="O34" t="s">
+        <v>334</v>
+      </c>
+      <c r="P34">
+        <v>29</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>331</v>
+      </c>
+      <c r="R34" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18">
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0030</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="5"/>
+        <v>a 3 deg.g64</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.g64</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="4"/>
+        <v>g64</v>
+      </c>
+      <c r="N35">
+        <v>5</v>
+      </c>
+      <c r="O35" t="s">
+        <v>335</v>
+      </c>
+      <c r="P35">
+        <v>30</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>331</v>
+      </c>
+      <c r="R35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18">
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0031</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="5"/>
+        <v>e 1.5 deg no OS.f97p50</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.f97p50</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="4"/>
+        <v>f97p50</v>
+      </c>
+      <c r="N36">
+        <v>5</v>
+      </c>
+      <c r="O36" t="s">
+        <v>336</v>
+      </c>
+      <c r="P36">
+        <v>31</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>337</v>
+      </c>
+      <c r="R36" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18">
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0032</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="5"/>
+        <v>d 1.5 deg OS.f97p50</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.f97p50</v>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="4"/>
+        <v>f97p50</v>
+      </c>
+      <c r="N37">
+        <v>5</v>
+      </c>
+      <c r="O37" t="s">
+        <v>338</v>
+      </c>
+      <c r="P37">
+        <v>32</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>337</v>
+      </c>
+      <c r="R37" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18">
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0033</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="5"/>
+        <v>c 2 deg (67%).f97p50</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).f97p50</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="4"/>
+        <v>f97p50</v>
+      </c>
+      <c r="N38">
+        <v>5</v>
+      </c>
+      <c r="O38" t="s">
+        <v>339</v>
+      </c>
+      <c r="P38">
+        <v>33</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>337</v>
+      </c>
+      <c r="R38" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18">
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0034</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="5"/>
+        <v>b 2 deg (50%).f97p50</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).f97p50</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="4"/>
+        <v>f97p50</v>
+      </c>
+      <c r="N39">
+        <v>5</v>
+      </c>
+      <c r="O39" t="s">
+        <v>340</v>
+      </c>
+      <c r="P39">
+        <v>34</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>337</v>
+      </c>
+      <c r="R39" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18">
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0035</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="5"/>
+        <v>a 3 deg.f97p50</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.f97p50</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="4"/>
+        <v>f97p50</v>
+      </c>
+      <c r="N40">
+        <v>5</v>
+      </c>
+      <c r="O40" t="s">
+        <v>341</v>
+      </c>
+      <c r="P40">
+        <v>35</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>337</v>
+      </c>
+      <c r="R40" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18">
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0036</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" ref="C41:C55" si="6">H41</f>
+        <v>e 1.5 deg no OS.f96p10</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.f96p10</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p10</v>
+      </c>
+      <c r="N41">
+        <v>5</v>
+      </c>
+      <c r="O41" t="s">
+        <v>342</v>
+      </c>
+      <c r="P41">
+        <v>36</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>343</v>
+      </c>
+      <c r="R41" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18">
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0037</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS.f96p10</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.f96p10</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p10</v>
+      </c>
+      <c r="N42">
+        <v>5</v>
+      </c>
+      <c r="O42" t="s">
+        <v>344</v>
+      </c>
+      <c r="P42">
+        <v>37</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>343</v>
+      </c>
+      <c r="R42" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18">
+      <c r="B43" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0038</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%).f96p10</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).f96p10</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p10</v>
+      </c>
+      <c r="N43">
+        <v>5</v>
+      </c>
+      <c r="O43" t="s">
+        <v>345</v>
+      </c>
+      <c r="P43">
+        <v>38</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>343</v>
+      </c>
+      <c r="R43" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18">
+      <c r="B44" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0039</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%).f96p10</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).f96p10</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p10</v>
+      </c>
+      <c r="N44">
+        <v>5</v>
+      </c>
+      <c r="O44" t="s">
+        <v>346</v>
+      </c>
+      <c r="P44">
+        <v>39</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>343</v>
+      </c>
+      <c r="R44" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18">
+      <c r="B45" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0040</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg.f96p10</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.f96p10</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p10</v>
+      </c>
+      <c r="N45">
+        <v>5</v>
+      </c>
+      <c r="O45" t="s">
+        <v>347</v>
+      </c>
+      <c r="P45">
+        <v>40</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>343</v>
+      </c>
+      <c r="R45" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18">
+      <c r="B46" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0041</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS.f96p90</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.f96p90</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p90</v>
+      </c>
+      <c r="N46">
+        <v>5</v>
+      </c>
+      <c r="O46" t="s">
+        <v>348</v>
+      </c>
+      <c r="P46">
+        <v>41</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>349</v>
+      </c>
+      <c r="R46" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18">
+      <c r="B47" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0042</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS.f96p90</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.f96p90</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p90</v>
+      </c>
+      <c r="N47">
+        <v>5</v>
+      </c>
+      <c r="O47" t="s">
+        <v>350</v>
+      </c>
+      <c r="P47">
+        <v>42</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>349</v>
+      </c>
+      <c r="R47" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18">
+      <c r="B48" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0043</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%).f96p90</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).f96p90</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p90</v>
+      </c>
+      <c r="N48">
+        <v>5</v>
+      </c>
+      <c r="O48" t="s">
+        <v>351</v>
+      </c>
+      <c r="P48">
+        <v>43</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>349</v>
+      </c>
+      <c r="R48" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18">
+      <c r="B49" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0044</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%).f96p90</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).f96p90</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p90</v>
+      </c>
+      <c r="N49">
+        <v>5</v>
+      </c>
+      <c r="O49" t="s">
+        <v>352</v>
+      </c>
+      <c r="P49">
+        <v>44</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>349</v>
+      </c>
+      <c r="R49" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="50" spans="2:18">
+      <c r="B50" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0045</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg.f96p90</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.f96p90</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="4"/>
+        <v>f96p90</v>
+      </c>
+      <c r="N50">
+        <v>5</v>
+      </c>
+      <c r="O50" t="s">
+        <v>353</v>
+      </c>
+      <c r="P50">
+        <v>45</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>349</v>
+      </c>
+      <c r="R50" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18">
+      <c r="B51" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0046</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="6"/>
+        <v>e 1.5 deg no OS.e3d</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.e3d</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="4"/>
+        <v>e3d</v>
+      </c>
+      <c r="N51">
+        <v>5</v>
+      </c>
+      <c r="O51" t="s">
+        <v>354</v>
+      </c>
+      <c r="P51">
+        <v>46</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>230</v>
+      </c>
+      <c r="R51" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18">
+      <c r="B52" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0047</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="6"/>
+        <v>d 1.5 deg OS.e3d</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.e3d</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="4"/>
+        <v>e3d</v>
+      </c>
+      <c r="N52">
+        <v>5</v>
+      </c>
+      <c r="O52" t="s">
+        <v>355</v>
+      </c>
+      <c r="P52">
+        <v>47</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>230</v>
+      </c>
+      <c r="R52" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18">
+      <c r="B53" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0048</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="6"/>
+        <v>c 2 deg (67%).e3d</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).e3d</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="4"/>
+        <v>e3d</v>
+      </c>
+      <c r="N53">
+        <v>5</v>
+      </c>
+      <c r="O53" t="s">
+        <v>356</v>
+      </c>
+      <c r="P53">
+        <v>48</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>230</v>
+      </c>
+      <c r="R53" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18">
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0049</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="6"/>
+        <v>b 2 deg (50%).e3d</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).e3d</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="4"/>
+        <v>e3d</v>
+      </c>
+      <c r="N54">
+        <v>5</v>
+      </c>
+      <c r="O54" t="s">
+        <v>357</v>
+      </c>
+      <c r="P54">
+        <v>49</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>230</v>
+      </c>
+      <c r="R54" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18">
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0050</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="6"/>
+        <v>a 3 deg.e3d</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.e3d</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="4"/>
+        <v>e3d</v>
+      </c>
+      <c r="N55">
+        <v>5</v>
+      </c>
+      <c r="O55" t="s">
+        <v>358</v>
+      </c>
+      <c r="P55">
+        <v>50</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>230</v>
+      </c>
+      <c r="R55" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18">
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0051</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" ref="C56:C60" si="7">H56</f>
+        <v>e 1.5 deg no OS.d9d</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="2"/>
+        <v>e 1.5 deg no OS.d9d</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="3"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="N56">
+        <v>5</v>
+      </c>
+      <c r="O56" t="s">
+        <v>359</v>
+      </c>
+      <c r="P56">
+        <v>51</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>231</v>
+      </c>
+      <c r="R56" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18">
+      <c r="B57" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0052</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="7"/>
+        <v>d 1.5 deg OS.d9d</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="2"/>
+        <v>d 1.5 deg OS.d9d</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="3"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="N57">
+        <v>5</v>
+      </c>
+      <c r="O57" t="s">
+        <v>360</v>
+      </c>
+      <c r="P57">
+        <v>52</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>231</v>
+      </c>
+      <c r="R57" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18">
+      <c r="B58" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0053</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="7"/>
+        <v>c 2 deg (67%).d9d</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="2"/>
+        <v>c 2 deg (67%).d9d</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="3"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="N58">
+        <v>5</v>
+      </c>
+      <c r="O58" t="s">
+        <v>361</v>
+      </c>
+      <c r="P58">
+        <v>53</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>231</v>
+      </c>
+      <c r="R58" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="2:18">
+      <c r="B59" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0054</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="7"/>
+        <v>b 2 deg (50%).d9d</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="2"/>
+        <v>b 2 deg (50%).d9d</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="3"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="N59">
+        <v>5</v>
+      </c>
+      <c r="O59" t="s">
+        <v>362</v>
+      </c>
+      <c r="P59">
+        <v>54</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>231</v>
+      </c>
+      <c r="R59" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="60" spans="2:18">
+      <c r="B60" t="str">
+        <f t="shared" si="0"/>
+        <v>vs~0055</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="7"/>
+        <v>a 3 deg.d9d</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="2"/>
+        <v>a 3 deg.d9d</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="3"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="4"/>
+        <v>d9d</v>
+      </c>
+      <c r="N60">
+        <v>5</v>
+      </c>
+      <c r="O60" t="s">
+        <v>363</v>
+      </c>
+      <c r="P60">
+        <v>55</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>231</v>
+      </c>
+      <c r="R60" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="61" spans="2:18">
+      <c r="B61" t="str">
+        <f t="shared" ref="B61:B75" si="8">"vs~"&amp;TEXT(P61,"0000")</f>
+        <v>vs~0056</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" ref="C61:C75" si="9">H61</f>
+        <v>e 1.5 deg no OS.c15d</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" ref="H61:H75" si="10">_xlfn.TEXTJOIN(".",TRUE,I61:J61)</f>
+        <v>e 1.5 deg no OS.c15d</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" ref="I61:I75" si="11">VLOOKUP(R61,$W$6:$X$12,2,FALSE)</f>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" ref="J61:J75" si="12">VLOOKUP(Q61,$T$6:$U$20,2,FALSE)</f>
+        <v>c15d</v>
+      </c>
+      <c r="N61">
+        <v>5</v>
+      </c>
+      <c r="O61" t="s">
+        <v>364</v>
+      </c>
+      <c r="P61">
+        <v>56</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>237</v>
+      </c>
+      <c r="R61" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="62" spans="2:18">
+      <c r="B62" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0057</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="9"/>
+        <v>d 1.5 deg OS.c15d</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="10"/>
+        <v>d 1.5 deg OS.c15d</v>
+      </c>
+      <c r="I62" t="str">
+        <f t="shared" si="11"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" si="12"/>
+        <v>c15d</v>
+      </c>
+      <c r="N62">
+        <v>5</v>
+      </c>
+      <c r="O62" t="s">
+        <v>365</v>
+      </c>
+      <c r="P62">
+        <v>57</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>237</v>
+      </c>
+      <c r="R62" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="63" spans="2:18">
+      <c r="B63" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0058</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="9"/>
+        <v>c 2 deg (67%).c15d</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="10"/>
+        <v>c 2 deg (67%).c15d</v>
+      </c>
+      <c r="I63" t="str">
+        <f t="shared" si="11"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J63" t="str">
+        <f t="shared" si="12"/>
+        <v>c15d</v>
+      </c>
+      <c r="N63">
+        <v>5</v>
+      </c>
+      <c r="O63" t="s">
+        <v>366</v>
+      </c>
+      <c r="P63">
+        <v>58</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>237</v>
+      </c>
+      <c r="R63" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="64" spans="2:18">
+      <c r="B64" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0059</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="9"/>
+        <v>b 2 deg (50%).c15d</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="10"/>
+        <v>b 2 deg (50%).c15d</v>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="11"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="12"/>
+        <v>c15d</v>
+      </c>
+      <c r="N64">
+        <v>5</v>
+      </c>
+      <c r="O64" t="s">
+        <v>367</v>
+      </c>
+      <c r="P64">
+        <v>59</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>237</v>
+      </c>
+      <c r="R64" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18">
+      <c r="B65" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0060</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="9"/>
+        <v>a 3 deg.c15d</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="10"/>
+        <v>a 3 deg.c15d</v>
+      </c>
+      <c r="I65" t="str">
+        <f t="shared" si="11"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J65" t="str">
+        <f t="shared" si="12"/>
+        <v>c15d</v>
+      </c>
+      <c r="N65">
+        <v>5</v>
+      </c>
+      <c r="O65" t="s">
+        <v>368</v>
+      </c>
+      <c r="P65">
+        <v>60</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>237</v>
+      </c>
+      <c r="R65" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18">
+      <c r="B66" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0061</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" si="9"/>
+        <v>e 1.5 deg no OS.b2w</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="10"/>
+        <v>e 1.5 deg no OS.b2w</v>
+      </c>
+      <c r="I66" t="str">
+        <f t="shared" si="11"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J66" t="str">
+        <f t="shared" si="12"/>
+        <v>b2w</v>
+      </c>
+      <c r="N66">
+        <v>5</v>
+      </c>
+      <c r="O66" t="s">
+        <v>369</v>
+      </c>
+      <c r="P66">
+        <v>61</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>232</v>
+      </c>
+      <c r="R66" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18">
+      <c r="B67" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0062</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="9"/>
+        <v>d 1.5 deg OS.b2w</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" si="10"/>
+        <v>d 1.5 deg OS.b2w</v>
+      </c>
+      <c r="I67" t="str">
+        <f t="shared" si="11"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J67" t="str">
+        <f t="shared" si="12"/>
+        <v>b2w</v>
+      </c>
+      <c r="N67">
+        <v>5</v>
+      </c>
+      <c r="O67" t="s">
+        <v>370</v>
+      </c>
+      <c r="P67">
+        <v>62</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>232</v>
+      </c>
+      <c r="R67" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="68" spans="2:18">
+      <c r="B68" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0063</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="9"/>
+        <v>c 2 deg (67%).b2w</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="10"/>
+        <v>c 2 deg (67%).b2w</v>
+      </c>
+      <c r="I68" t="str">
+        <f t="shared" si="11"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J68" t="str">
+        <f t="shared" si="12"/>
+        <v>b2w</v>
+      </c>
+      <c r="N68">
+        <v>5</v>
+      </c>
+      <c r="O68" t="s">
+        <v>371</v>
+      </c>
+      <c r="P68">
+        <v>63</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>232</v>
+      </c>
+      <c r="R68" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18">
+      <c r="B69" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0064</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="9"/>
+        <v>b 2 deg (50%).b2w</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="10"/>
+        <v>b 2 deg (50%).b2w</v>
+      </c>
+      <c r="I69" t="str">
+        <f t="shared" si="11"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J69" t="str">
+        <f t="shared" si="12"/>
+        <v>b2w</v>
+      </c>
+      <c r="N69">
+        <v>5</v>
+      </c>
+      <c r="O69" t="s">
+        <v>372</v>
+      </c>
+      <c r="P69">
+        <v>64</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>232</v>
+      </c>
+      <c r="R69" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18">
+      <c r="B70" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0065</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="9"/>
+        <v>a 3 deg.b2w</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="10"/>
+        <v>a 3 deg.b2w</v>
+      </c>
+      <c r="I70" t="str">
+        <f t="shared" si="11"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J70" t="str">
+        <f t="shared" si="12"/>
+        <v>b2w</v>
+      </c>
+      <c r="N70">
+        <v>5</v>
+      </c>
+      <c r="O70" t="s">
+        <v>373</v>
+      </c>
+      <c r="P70">
+        <v>65</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>232</v>
+      </c>
+      <c r="R70" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18">
+      <c r="B71" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0066</v>
+      </c>
+      <c r="C71" t="str">
+        <f t="shared" si="9"/>
+        <v>e 1.5 deg no OS.a2w2d</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="10"/>
+        <v>e 1.5 deg no OS.a2w2d</v>
+      </c>
+      <c r="I71" t="str">
+        <f t="shared" si="11"/>
+        <v>e 1.5 deg no OS</v>
+      </c>
+      <c r="J71" t="str">
+        <f t="shared" si="12"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="N71">
+        <v>5</v>
+      </c>
+      <c r="O71" t="s">
+        <v>374</v>
+      </c>
+      <c r="P71">
+        <v>66</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>233</v>
+      </c>
+      <c r="R71" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18">
+      <c r="B72" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0067</v>
+      </c>
+      <c r="C72" t="str">
+        <f t="shared" si="9"/>
+        <v>d 1.5 deg OS.a2w2d</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="10"/>
+        <v>d 1.5 deg OS.a2w2d</v>
+      </c>
+      <c r="I72" t="str">
+        <f t="shared" si="11"/>
+        <v>d 1.5 deg OS</v>
+      </c>
+      <c r="J72" t="str">
+        <f t="shared" si="12"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="N72">
+        <v>5</v>
+      </c>
+      <c r="O72" t="s">
+        <v>375</v>
+      </c>
+      <c r="P72">
+        <v>67</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>233</v>
+      </c>
+      <c r="R72" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18">
+      <c r="B73" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0068</v>
+      </c>
+      <c r="C73" t="str">
+        <f t="shared" si="9"/>
+        <v>c 2 deg (67%).a2w2d</v>
+      </c>
+      <c r="H73" t="str">
+        <f t="shared" si="10"/>
+        <v>c 2 deg (67%).a2w2d</v>
+      </c>
+      <c r="I73" t="str">
+        <f t="shared" si="11"/>
+        <v>c 2 deg (67%)</v>
+      </c>
+      <c r="J73" t="str">
+        <f t="shared" si="12"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="N73">
+        <v>5</v>
+      </c>
+      <c r="O73" t="s">
+        <v>376</v>
+      </c>
+      <c r="P73">
+        <v>68</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>233</v>
+      </c>
+      <c r="R73" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18">
+      <c r="B74" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0069</v>
+      </c>
+      <c r="C74" t="str">
+        <f t="shared" si="9"/>
+        <v>b 2 deg (50%).a2w2d</v>
+      </c>
+      <c r="H74" t="str">
+        <f t="shared" si="10"/>
+        <v>b 2 deg (50%).a2w2d</v>
+      </c>
+      <c r="I74" t="str">
+        <f t="shared" si="11"/>
+        <v>b 2 deg (50%)</v>
+      </c>
+      <c r="J74" t="str">
+        <f t="shared" si="12"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="N74">
+        <v>5</v>
+      </c>
+      <c r="O74" t="s">
+        <v>377</v>
+      </c>
+      <c r="P74">
+        <v>69</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>233</v>
+      </c>
+      <c r="R74" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18">
+      <c r="B75" t="str">
+        <f t="shared" si="8"/>
+        <v>vs~0070</v>
+      </c>
+      <c r="C75" t="str">
+        <f t="shared" si="9"/>
+        <v>a 3 deg.a2w2d</v>
+      </c>
+      <c r="H75" t="str">
+        <f t="shared" si="10"/>
+        <v>a 3 deg.a2w2d</v>
+      </c>
+      <c r="I75" t="str">
+        <f t="shared" si="11"/>
+        <v>a 3 deg</v>
+      </c>
+      <c r="J75" t="str">
+        <f t="shared" si="12"/>
+        <v>a2w2d</v>
+      </c>
+      <c r="N75">
+        <v>5</v>
+      </c>
+      <c r="O75" t="s">
+        <v>378</v>
+      </c>
+      <c r="P75">
+        <v>70</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>233</v>
+      </c>
+      <c r="R75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D59:D68">
+    <sortCondition ref="D59:D68"/>
+  </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -2738,10 +7630,10 @@
         <v>10</v>
       </c>
       <c r="Q2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -2749,16 +7641,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="K3" t="s">
         <v>8</v>
       </c>
       <c r="N3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -2766,19 +7658,19 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="K4" t="s">
         <v>8</v>
       </c>
       <c r="N4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U4" s="8"/>
     </row>
@@ -2787,49 +7679,49 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="I5" t="s">
-        <v>178</v>
+        <v>261</v>
       </c>
       <c r="K5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" t="s">
         <v>81</v>
       </c>
-      <c r="N5" t="s">
-        <v>82</v>
-      </c>
       <c r="T5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D6" s="2"/>
       <c r="H6" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N6" t="s">
         <v>42</v>
       </c>
       <c r="Q6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2839,13 +7731,13 @@
         <v>5</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="K7" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="N7" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2855,13 +7747,13 @@
         <v>5</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="K8" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2871,16 +7763,16 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>292</v>
       </c>
       <c r="N9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -2888,22 +7780,22 @@
         <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
         <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N10" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" t="s">
         <v>46</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>47</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -2911,50 +7803,78 @@
         <v>29</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I11" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="K11" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" t="s">
+        <v>84</v>
+      </c>
+      <c r="N12" t="s">
         <v>49</v>
       </c>
-      <c r="K12" t="s">
-        <v>85</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q12" t="s">
         <v>50</v>
-      </c>
-      <c r="P12" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q13" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K14" t="s">
+        <v>292</v>
+      </c>
+      <c r="N14" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="K15" t="s">
+        <v>292</v>
+      </c>
+      <c r="N15" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2966,7 +7886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A8EC7F-95E3-4526-8B78-C58A96098159}">
   <dimension ref="C1:K3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2984,15 +7904,15 @@
   <sheetData>
     <row r="1" spans="3:11">
       <c r="C1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="3:11">
       <c r="C2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" t="s">
         <v>105</v>
-      </c>
-      <c r="D2" t="s">
-        <v>106</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>2</v>
@@ -3001,16 +7921,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
         <v>107</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>108</v>
-      </c>
-      <c r="J2" t="s">
-        <v>109</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -3018,25 +7938,25 @@
     </row>
     <row r="3" spans="3:11">
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" t="s">
         <v>110</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" t="s">
         <v>111</v>
       </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" t="s">
-        <v>112</v>
-      </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3046,35 +7966,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D44EBE-400A-4EA2-9DA1-076783A77DFC}">
-  <dimension ref="A3:S6"/>
+  <dimension ref="A3:S23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="30.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="255.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.53125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.53125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.9296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="19" width="19.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:19" ht="17.25" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>181</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" thickTop="1" thickBot="1">
@@ -3124,16 +8026,16 @@
         <v>10</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3146,13 +8048,13 @@
       </c>
       <c r="G5" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,CSET_MAP!$A$3:$A$43)</f>
-        <v>Elec-220V,Elec-400V,Elec-380V,Elec-225V,Elec-330V,Elec-275V,Elec-420V,Elec-300V,Elec-500V,Elec-750V,Elec-450V,Elec-515V,Elec-525V,Elec-320V,Elec-150V,Elec-270V,Elec-350V,Elec-250V,Elec-200V,Elec-236V,Elec-600V,Solar elec,Wind elec,fossil,renewable,bioenergy,hydrogen,nuclear,ELC,buildings,industry,transport,EVs</v>
+        <v>Elec-220V,Elec-400V,Elec-380V,Elec-225V,Elec-330V,Elec-275V,Elec-420V,Elec-300V,Elec-500V,Elec-750V,Elec-450V,Elec-515V,Elec-525V,Elec-320V,Elec-150V,Elec-270V,Elec-350V,Elec-250V,Elec-200V,Elec-236V,Elec-600V,Solar elec,Wind elec,hydrogen,ELC,buildings,industry,transport,EVs,fossil,renewable,bioenergy,nuclear</v>
       </c>
       <c r="J5" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="M5" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -3160,7 +8062,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="B6" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,PSet_MAP!$A$3:$A$49)</f>
@@ -3168,15 +8070,253 @@
       </c>
       <c r="G6" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,CSET_MAP!$A$3:$A$43)</f>
-        <v>Elec-220V,Elec-400V,Elec-380V,Elec-225V,Elec-330V,Elec-275V,Elec-420V,Elec-300V,Elec-500V,Elec-750V,Elec-450V,Elec-515V,Elec-525V,Elec-320V,Elec-150V,Elec-270V,Elec-350V,Elec-250V,Elec-200V,Elec-236V,Elec-600V,Solar elec,Wind elec,fossil,renewable,bioenergy,hydrogen,nuclear,ELC,buildings,industry,transport,EVs</v>
+        <v>Elec-220V,Elec-400V,Elec-380V,Elec-225V,Elec-330V,Elec-275V,Elec-420V,Elec-300V,Elec-500V,Elec-750V,Elec-450V,Elec-515V,Elec-525V,Elec-320V,Elec-150V,Elec-270V,Elec-350V,Elec-250V,Elec-200V,Elec-236V,Elec-600V,Solar elec,Wind elec,hydrogen,ELC,buildings,industry,transport,EVs,fossil,renewable,bioenergy,nuclear</v>
       </c>
       <c r="J6" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="M6" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="S6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="17.25" thickBot="1">
+      <c r="A10" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15" thickTop="1" thickBot="1">
+      <c r="A11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="str">
+        <f>H13</f>
+        <v>bioenergy,coal,gas,geothermal,hydro,hydrogen,nuclear,oil,solar,windon,windoff</v>
+      </c>
+      <c r="H13" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,CName_MAP!$A$3:$A$16)</f>
+        <v>bioenergy,coal,gas,geothermal,hydro,hydrogen,nuclear,oil,solar,windon,windoff</v>
+      </c>
+      <c r="J13" t="s">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s">
+        <v>274</v>
+      </c>
+      <c r="S13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" t="str">
+        <f>B5</f>
+        <v>CCGT,Int Comb,Gas_Oil Steam,OCGT (Peaker),Subcritical Coal,Supercritical Coal,IGCC,Bio Power,Solar Util,Wind onshore,Wind offshore,Geothermal P,Hydro Dam,Hydro RoR,Nuclear P,Nuclear SMR,Hydro pumped stg,Util Batt Stg,EV Batt,Demand,Transformers Dn,Transformers Up,Grid-220V,Grid-400V,Grid-380V,Grid-225V,Grid-330V,Grid-275V,Grid-420V,Grid-300V,Grid-500V,Grid-750V,Grid-450V,Grid-515V,Grid-525V,Grid-320V,Grid-150V,Grid-270V,Grid-350V,Grid-250V,Grid-200V,Grid-236V,Grid-600V,Aggregators,DUMMY_IMP</v>
+      </c>
+      <c r="H14" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,CName_MAP!$A$3:$A$16)</f>
+        <v>bioenergy,coal,gas,geothermal,hydro,hydrogen,nuclear,oil,solar,windon,windoff</v>
+      </c>
+      <c r="J14" t="s">
+        <v>160</v>
+      </c>
+      <c r="M14" t="s">
+        <v>275</v>
+      </c>
+      <c r="S14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,PSet_MAP!$A$3:$A$49)</f>
+        <v>CCGT,Int Comb,Gas_Oil Steam,OCGT (Peaker),Subcritical Coal,Supercritical Coal,IGCC,Bio Power,Solar Util,Wind onshore,Wind offshore,Geothermal P,Hydro Dam,Hydro RoR,Nuclear P,Nuclear SMR,Hydro pumped stg,Util Batt Stg,EV Batt,Demand,Transformers Dn,Transformers Up,Grid-220V,Grid-400V,Grid-380V,Grid-225V,Grid-330V,Grid-275V,Grid-420V,Grid-300V,Grid-500V,Grid-750V,Grid-450V,Grid-515V,Grid-525V,Grid-320V,Grid-150V,Grid-270V,Grid-350V,Grid-250V,Grid-200V,Grid-236V,Grid-600V,Aggregators,DUMMY_IMP</v>
+      </c>
+      <c r="G16" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,CSET_MAP!$A$3:$A$31)</f>
+        <v>Elec-220V,Elec-400V,Elec-380V,Elec-225V,Elec-330V,Elec-275V,Elec-420V,Elec-300V,Elec-500V,Elec-750V,Elec-450V,Elec-515V,Elec-525V,Elec-320V,Elec-150V,Elec-270V,Elec-350V,Elec-250V,Elec-200V,Elec-236V,Elec-600V,Solar elec,Wind elec,hydrogen,ELC,buildings,industry,transport,EVs</v>
+      </c>
+      <c r="J16" t="s">
+        <v>160</v>
+      </c>
+      <c r="M16" t="s">
+        <v>282</v>
+      </c>
+      <c r="S16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,PSet_MAP!$A$3:$A$49)</f>
+        <v>CCGT,Int Comb,Gas_Oil Steam,OCGT (Peaker),Subcritical Coal,Supercritical Coal,IGCC,Bio Power,Solar Util,Wind onshore,Wind offshore,Geothermal P,Hydro Dam,Hydro RoR,Nuclear P,Nuclear SMR,Hydro pumped stg,Util Batt Stg,EV Batt,Demand,Transformers Dn,Transformers Up,Grid-220V,Grid-400V,Grid-380V,Grid-225V,Grid-330V,Grid-275V,Grid-420V,Grid-300V,Grid-500V,Grid-750V,Grid-450V,Grid-515V,Grid-525V,Grid-320V,Grid-150V,Grid-270V,Grid-350V,Grid-250V,Grid-200V,Grid-236V,Grid-600V,Aggregators,DUMMY_IMP</v>
+      </c>
+      <c r="G17" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,CSET_MAP!$A$3:$A$31)</f>
+        <v>Elec-220V,Elec-400V,Elec-380V,Elec-225V,Elec-330V,Elec-275V,Elec-420V,Elec-300V,Elec-500V,Elec-750V,Elec-450V,Elec-515V,Elec-525V,Elec-320V,Elec-150V,Elec-270V,Elec-350V,Elec-250V,Elec-200V,Elec-236V,Elec-600V,Solar elec,Wind elec,hydrogen,ELC,buildings,industry,transport,EVs</v>
+      </c>
+      <c r="J17" t="s">
+        <v>160</v>
+      </c>
+      <c r="M17" t="s">
+        <v>283</v>
+      </c>
+      <c r="S17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="str">
+        <f>H19</f>
+        <v>hydrogen</v>
+      </c>
+      <c r="H19" t="s">
+        <v>185</v>
+      </c>
+      <c r="J19" t="s">
+        <v>160</v>
+      </c>
+      <c r="M19" t="s">
+        <v>274</v>
+      </c>
+      <c r="S19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20" t="s">
+        <v>185</v>
+      </c>
+      <c r="G20" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,CSET_MAP!$A$3:$A$43)</f>
+        <v>Elec-220V,Elec-400V,Elec-380V,Elec-225V,Elec-330V,Elec-275V,Elec-420V,Elec-300V,Elec-500V,Elec-750V,Elec-450V,Elec-515V,Elec-525V,Elec-320V,Elec-150V,Elec-270V,Elec-350V,Elec-250V,Elec-200V,Elec-236V,Elec-600V,Solar elec,Wind elec,hydrogen,ELC,buildings,industry,transport,EVs,fossil,renewable,bioenergy,nuclear</v>
+      </c>
+      <c r="J20" t="s">
+        <v>160</v>
+      </c>
+      <c r="M20" t="s">
+        <v>284</v>
+      </c>
+      <c r="S20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" t="s">
+        <v>185</v>
+      </c>
+      <c r="H23" t="s">
+        <v>185</v>
+      </c>
+      <c r="J23" t="s">
+        <v>160</v>
+      </c>
+      <c r="M23" t="s">
+        <v>278</v>
+      </c>
+      <c r="S23">
         <v>-1</v>
       </c>
     </row>
@@ -3185,7 +8325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C47"/>
@@ -3214,7 +8354,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3" t="str">
         <f>A3</f>
@@ -3223,7 +8363,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B47" si="0">A4</f>
@@ -3232,7 +8372,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
@@ -3241,7 +8381,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
@@ -3250,7 +8390,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
@@ -3259,7 +8399,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
@@ -3268,7 +8408,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
@@ -3277,7 +8417,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
@@ -3286,7 +8426,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
@@ -3295,25 +8435,23 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" t="str">
-        <f t="shared" si="0"/>
-        <v>Wind onshore</v>
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" t="str">
-        <f t="shared" si="0"/>
-        <v>Wind offshore</v>
+        <v>95</v>
+      </c>
+      <c r="B13" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
@@ -3322,7 +8460,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
@@ -3331,7 +8469,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
@@ -3340,7 +8478,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
@@ -3349,7 +8487,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
@@ -3358,7 +8496,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
@@ -3367,7 +8505,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
@@ -3376,7 +8514,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
@@ -3385,7 +8523,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
@@ -3394,7 +8532,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
@@ -3403,7 +8541,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
@@ -3412,7 +8550,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
@@ -3421,7 +8559,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
@@ -3430,7 +8568,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
@@ -3439,7 +8577,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
@@ -3448,7 +8586,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
@@ -3457,7 +8595,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
@@ -3466,7 +8604,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>
@@ -3475,7 +8613,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="0"/>
@@ -3484,7 +8622,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="0"/>
@@ -3493,7 +8631,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="0"/>
@@ -3502,7 +8640,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
@@ -3511,7 +8649,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="0"/>
@@ -3520,7 +8658,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="0"/>
@@ -3529,7 +8667,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="0"/>
@@ -3538,7 +8676,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
@@ -3547,7 +8685,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="0"/>
@@ -3556,7 +8694,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="0"/>
@@ -3565,7 +8703,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
@@ -3574,7 +8712,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="0"/>
@@ -3583,7 +8721,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="0"/>
@@ -3592,7 +8730,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="0"/>
@@ -3601,7 +8739,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
@@ -3610,7 +8748,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="0"/>
@@ -3623,7 +8761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E766D8-7F73-4A5A-98A5-9C85D527817F}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -3633,12 +8771,12 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -3649,7 +8787,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="B3" t="str">
         <f>A3</f>
@@ -3658,16 +8796,16 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" ref="B4:B35" si="0">A4</f>
+        <f t="shared" ref="B4:B23" si="0">A4</f>
         <v>Elec-400V</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
@@ -3676,7 +8814,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
@@ -3685,7 +8823,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
@@ -3694,7 +8832,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
@@ -3703,7 +8841,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
@@ -3712,7 +8850,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
@@ -3721,7 +8859,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
@@ -3730,7 +8868,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
@@ -3739,7 +8877,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
@@ -3748,7 +8886,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
@@ -3757,7 +8895,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
@@ -3766,7 +8904,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
@@ -3775,7 +8913,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
@@ -3784,7 +8922,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
@@ -3793,7 +8931,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
@@ -3802,7 +8940,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
@@ -3811,7 +8949,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
@@ -3820,7 +8958,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
@@ -3829,7 +8967,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
@@ -3838,110 +8976,107 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>224</v>
-      </c>
-      <c r="B24" t="str">
-        <f t="shared" si="0"/>
-        <v>Solar elec</v>
+        <v>202</v>
+      </c>
+      <c r="B24" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B25" t="str">
-        <f t="shared" si="0"/>
-        <v>Wind elec</v>
+        <v>203</v>
+      </c>
+      <c r="B25" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="0"/>
-        <v>fossil</v>
+        <f t="shared" ref="B26" si="1">A26</f>
+        <v>hydrogen</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>226</v>
-      </c>
-      <c r="B27" t="str">
-        <f t="shared" si="0"/>
-        <v>renewable</v>
+        <v>187</v>
+      </c>
+      <c r="B27" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="0"/>
-        <v>bioenergy</v>
+        <f t="shared" ref="B28:B35" si="2">A28</f>
+        <v>buildings</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="0"/>
-        <v>hydrogen</v>
+        <f t="shared" si="2"/>
+        <v>industry</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B30" t="str">
-        <f t="shared" si="0"/>
-        <v>nuclear</v>
+        <f t="shared" si="2"/>
+        <v>transport</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B31" t="str">
-        <f t="shared" si="0"/>
-        <v>ELC</v>
+        <f t="shared" si="2"/>
+        <v>EVs</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>210</v>
-      </c>
-      <c r="B32" t="str">
-        <f t="shared" si="0"/>
-        <v>buildings</v>
+      <c r="A32" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>fossil</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>211</v>
-      </c>
-      <c r="B33" t="str">
-        <f t="shared" si="0"/>
-        <v>industry</v>
+      <c r="A33" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>renewable</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>212</v>
-      </c>
-      <c r="B34" t="str">
-        <f t="shared" si="0"/>
-        <v>transport</v>
+      <c r="A34" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>bioenergy</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>213</v>
-      </c>
-      <c r="B35" t="str">
-        <f t="shared" si="0"/>
-        <v>EVs</v>
+      <c r="A35" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B35" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>nuclear</v>
       </c>
     </row>
   </sheetData>
@@ -3949,10 +9084,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.59765625" bestFit="1" customWidth="1"/>
@@ -3977,13 +9112,110 @@
         <v>10</v>
       </c>
     </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" t="str">
+        <f>A3</f>
+        <v>bioenergy</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" ref="B4:B11" si="0">A4</f>
+        <v>coal</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>gas</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>geothermal</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>hydro</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>hydrogen</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>nuclear</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>oil</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>solar</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" t="s">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32957E82-8232-40A9-A839-CC5F79005B92}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C10"/>
@@ -3996,48 +9228,48 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C5" t="str">
         <f>LEFT(B5,2)</f>
@@ -4046,10 +9278,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" ref="C6:C10" si="0">LEFT(B6,2)</f>
@@ -4058,10 +9290,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -4070,10 +9302,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -4082,10 +9314,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -4094,711 +9326,14 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
         <v>S6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.46484375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.53125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A1" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" thickBot="1">
-      <c r="A2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="str">
-        <f>D5</f>
-        <v>CCGT</v>
-      </c>
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="str">
-        <f t="shared" ref="C6:C49" si="0">D6</f>
-        <v>Int Comb</v>
-      </c>
-      <c r="D6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="str">
-        <f t="shared" si="0"/>
-        <v>Gas_Oil Steam</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="str">
-        <f t="shared" si="0"/>
-        <v>OCGT (Peaker)</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="str">
-        <f t="shared" si="0"/>
-        <v>Subcritical Coal</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="str">
-        <f t="shared" si="0"/>
-        <v>Supercritical Coal</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="str">
-        <f t="shared" si="0"/>
-        <v>IGCC</v>
-      </c>
-      <c r="D11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="str">
-        <f t="shared" si="0"/>
-        <v>Bio Power</v>
-      </c>
-      <c r="D12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="str">
-        <f t="shared" si="0"/>
-        <v>Solar Util</v>
-      </c>
-      <c r="D13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="str">
-        <f t="shared" si="0"/>
-        <v>Wind onshore</v>
-      </c>
-      <c r="D14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="str">
-        <f t="shared" si="0"/>
-        <v>Wind offshore</v>
-      </c>
-      <c r="D15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="str">
-        <f t="shared" si="0"/>
-        <v>Geothermal P</v>
-      </c>
-      <c r="D16" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="str">
-        <f t="shared" si="0"/>
-        <v>Hydro Dam</v>
-      </c>
-      <c r="D17" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="str">
-        <f t="shared" si="0"/>
-        <v>Hydro RoR</v>
-      </c>
-      <c r="D18" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="str">
-        <f t="shared" si="0"/>
-        <v>Nuclear P</v>
-      </c>
-      <c r="D19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="str">
-        <f t="shared" si="0"/>
-        <v>Nuclear SMR</v>
-      </c>
-      <c r="D20" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="str">
-        <f t="shared" si="0"/>
-        <v>Hydro pumped stg</v>
-      </c>
-      <c r="D21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="str">
-        <f t="shared" si="0"/>
-        <v>Util Batt Stg</v>
-      </c>
-      <c r="D22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" t="str">
-        <f t="shared" si="0"/>
-        <v>EV Batt</v>
-      </c>
-      <c r="D23" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="str">
-        <f t="shared" si="0"/>
-        <v>Demand</v>
-      </c>
-      <c r="D24" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="str">
-        <f t="shared" si="0"/>
-        <v>Transformers Dn</v>
-      </c>
-      <c r="D25" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="str">
-        <f t="shared" si="0"/>
-        <v>Transformers Up</v>
-      </c>
-      <c r="D26" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-220V</v>
-      </c>
-      <c r="D27" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-400V</v>
-      </c>
-      <c r="D28" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-380V</v>
-      </c>
-      <c r="D29" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-225V</v>
-      </c>
-      <c r="D30" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-330V</v>
-      </c>
-      <c r="D31" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-275V</v>
-      </c>
-      <c r="D32" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-420V</v>
-      </c>
-      <c r="D33" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-300V</v>
-      </c>
-      <c r="D34" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-500V</v>
-      </c>
-      <c r="D35" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-750V</v>
-      </c>
-      <c r="D36" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-450V</v>
-      </c>
-      <c r="D37" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-515V</v>
-      </c>
-      <c r="D38" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-525V</v>
-      </c>
-      <c r="D39" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-320V</v>
-      </c>
-      <c r="D40" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-150V</v>
-      </c>
-      <c r="D41" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-270V</v>
-      </c>
-      <c r="D42" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-350V</v>
-      </c>
-      <c r="D43" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-250V</v>
-      </c>
-      <c r="D44" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-200V</v>
-      </c>
-      <c r="D45" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-236V</v>
-      </c>
-      <c r="D46" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-600V</v>
-      </c>
-      <c r="D47" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" t="str">
-        <f t="shared" si="0"/>
-        <v>Aggregators</v>
-      </c>
-      <c r="D48" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" t="str">
-        <f t="shared" si="0"/>
-        <v>DUMMY_IMP</v>
-      </c>
-      <c r="D49" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" t="s">
-        <v>149</v>
-      </c>
-      <c r="F50" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" t="s">
-        <v>150</v>
-      </c>
-      <c r="F51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
-        <v>70</v>
-      </c>
-      <c r="B52" t="s">
-        <v>152</v>
-      </c>
-      <c r="C52" t="s">
-        <v>147</v>
-      </c>
-      <c r="E52" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" t="s">
-        <v>152</v>
-      </c>
-      <c r="C53" t="s">
-        <v>148</v>
-      </c>
-      <c r="E53" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
-        <v>70</v>
-      </c>
-      <c r="B54" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" t="s">
-        <v>102</v>
-      </c>
-      <c r="C55" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ESP/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ESP/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFA3B6F-77C9-4026-A7F7-2B3175ECC1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB1C8A7-4808-4116-B649-64C70DAF59A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="418">
   <si>
     <t>Unit</t>
   </si>
@@ -867,9 +867,6 @@
     <t>ar6_r10</t>
   </si>
   <si>
-    <t>ELC,ELC_???-???*,e[_]*</t>
-  </si>
-  <si>
     <t>*ccs</t>
   </si>
   <si>
@@ -1239,13 +1236,106 @@
     <t>g64</t>
   </si>
   <si>
-    <t>f97p50</t>
-  </si>
-  <si>
     <t>f96p10</t>
   </si>
   <si>
     <t>f96p90</t>
+  </si>
+  <si>
+    <t>f96p50</t>
+  </si>
+  <si>
+    <t>ELC,ELC_???[_]???*,e[_]*</t>
+  </si>
+  <si>
+    <t>IRE</t>
+  </si>
+  <si>
+    <t>g[_]*</t>
+  </si>
+  <si>
+    <t>Grid Capacity</t>
+  </si>
+  <si>
+    <t>Grid New Capacity</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>e_dem*</t>
+  </si>
+  <si>
+    <t>Industry and Buildings</t>
+  </si>
+  <si>
+    <t>ev_bat*</t>
+  </si>
+  <si>
+    <t>H2Prd*</t>
+  </si>
+  <si>
+    <t>e_dem*,ev_bat*,H2Prd*</t>
+  </si>
+  <si>
+    <t>e*</t>
+  </si>
+  <si>
+    <t>~tradeflow_exp</t>
+  </si>
+  <si>
+    <t>Internal variable to create Grid-level trade flows</t>
+  </si>
+  <si>
+    <t>p,c</t>
+  </si>
+  <si>
+    <t>~tradeflow_imp</t>
+  </si>
+  <si>
+    <t>ELC_???[_]???*,e[_]*</t>
+  </si>
+  <si>
+    <t>VerveStacks</t>
+  </si>
+  <si>
+    <t>Tech_origin</t>
+  </si>
+  <si>
+    <t>ep_*</t>
+  </si>
+  <si>
+    <t>GEM_operating</t>
+  </si>
+  <si>
+    <t>en_pc_*</t>
+  </si>
+  <si>
+    <t>GEM_pre-constr</t>
+  </si>
+  <si>
+    <t>ep_m_*</t>
+  </si>
+  <si>
+    <t>GEM_mothballed</t>
+  </si>
+  <si>
+    <t>en_a_*</t>
+  </si>
+  <si>
+    <t>GEM_announced</t>
+  </si>
+  <si>
+    <t>en_can_*</t>
+  </si>
+  <si>
+    <t>GEM_cancelled</t>
+  </si>
+  <si>
+    <t>en_she_*</t>
+  </si>
+  <si>
+    <t>GEM_shelved</t>
   </si>
 </sst>
 </file>
@@ -2311,10 +2401,10 @@
         <v>11</v>
       </c>
       <c r="T16" t="s">
+        <v>262</v>
+      </c>
+      <c r="U16" t="s">
         <v>263</v>
-      </c>
-      <c r="U16" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -3821,7 +3911,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
@@ -4427,7 +4517,7 @@
         <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C50" t="s">
         <v>132</v>
@@ -4441,7 +4531,7 @@
         <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C51" t="s">
         <v>133</v>
@@ -4509,6 +4599,116 @@
       </c>
       <c r="C56" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>392</v>
+      </c>
+      <c r="B57" t="s">
+        <v>393</v>
+      </c>
+      <c r="C57" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>392</v>
+      </c>
+      <c r="B58" t="s">
+        <v>395</v>
+      </c>
+      <c r="C58" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>392</v>
+      </c>
+      <c r="B59" t="s">
+        <v>396</v>
+      </c>
+      <c r="C59" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>405</v>
+      </c>
+      <c r="B60" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>405</v>
+      </c>
+      <c r="B61" t="s">
+        <v>406</v>
+      </c>
+      <c r="C61" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>405</v>
+      </c>
+      <c r="B62" t="s">
+        <v>408</v>
+      </c>
+      <c r="C62" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>405</v>
+      </c>
+      <c r="B63" t="s">
+        <v>410</v>
+      </c>
+      <c r="C63" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>405</v>
+      </c>
+      <c r="B64" t="s">
+        <v>412</v>
+      </c>
+      <c r="C64" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>405</v>
+      </c>
+      <c r="B65" t="s">
+        <v>414</v>
+      </c>
+      <c r="C65" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>405</v>
+      </c>
+      <c r="B66" t="s">
+        <v>416</v>
+      </c>
+      <c r="C66" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -4773,7 +4973,7 @@
         <v>63</v>
       </c>
       <c r="O4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="2:24">
@@ -4801,19 +5001,19 @@
         <v>sg_timeslice</v>
       </c>
       <c r="N5" t="s">
+        <v>296</v>
+      </c>
+      <c r="O5" t="s">
         <v>297</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>298</v>
-      </c>
-      <c r="P5" t="s">
-        <v>299</v>
       </c>
       <c r="Q5" t="s">
         <v>124</v>
       </c>
       <c r="R5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="2:24">
@@ -4844,7 +5044,7 @@
         <v>5</v>
       </c>
       <c r="O6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -4853,16 +5053,16 @@
         <v>238</v>
       </c>
       <c r="R6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T6" t="s">
         <v>238</v>
       </c>
       <c r="U6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="W6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="X6" t="s">
         <v>258</v>
@@ -4896,7 +5096,7 @@
         <v>5</v>
       </c>
       <c r="O7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P7">
         <v>2</v>
@@ -4905,16 +5105,16 @@
         <v>238</v>
       </c>
       <c r="R7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="U7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="W7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="X7" t="s">
         <v>257</v>
@@ -4948,7 +5148,7 @@
         <v>5</v>
       </c>
       <c r="O8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P8">
         <v>3</v>
@@ -4957,16 +5157,16 @@
         <v>238</v>
       </c>
       <c r="R8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="W8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="X8" t="s">
         <v>256</v>
@@ -5000,7 +5200,7 @@
         <v>5</v>
       </c>
       <c r="O9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P9">
         <v>4</v>
@@ -5009,16 +5209,16 @@
         <v>238</v>
       </c>
       <c r="R9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="T9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="U9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="W9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="X9" t="s">
         <v>255</v>
@@ -5052,7 +5252,7 @@
         <v>5</v>
       </c>
       <c r="O10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P10">
         <v>5</v>
@@ -5061,16 +5261,16 @@
         <v>238</v>
       </c>
       <c r="R10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="U10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="W10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="X10" t="s">
         <v>259</v>
@@ -5101,22 +5301,22 @@
         <v>5</v>
       </c>
       <c r="O11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P11">
         <v>6</v>
       </c>
       <c r="Q11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="U11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" spans="2:24">
@@ -5144,22 +5344,22 @@
         <v>5</v>
       </c>
       <c r="O12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P12">
         <v>7</v>
       </c>
       <c r="Q12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="U12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="2:24">
@@ -5187,22 +5387,22 @@
         <v>5</v>
       </c>
       <c r="O13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P13">
         <v>8</v>
       </c>
       <c r="Q13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="U13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" spans="2:24">
@@ -5230,22 +5430,22 @@
         <v>5</v>
       </c>
       <c r="O14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P14">
         <v>9</v>
       </c>
       <c r="Q14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="T14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U14" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15" spans="2:24">
@@ -5273,16 +5473,16 @@
         <v>5</v>
       </c>
       <c r="O15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P15">
         <v>10</v>
       </c>
       <c r="Q15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T15" t="s">
         <v>230</v>
@@ -5316,16 +5516,16 @@
         <v>5</v>
       </c>
       <c r="O16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P16">
         <v>11</v>
       </c>
       <c r="Q16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T16" t="s">
         <v>231</v>
@@ -5359,16 +5559,16 @@
         <v>5</v>
       </c>
       <c r="O17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P17">
         <v>12</v>
       </c>
       <c r="Q17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T17" t="s">
         <v>237</v>
@@ -5402,16 +5602,16 @@
         <v>5</v>
       </c>
       <c r="O18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P18">
         <v>13</v>
       </c>
       <c r="Q18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T18" t="s">
         <v>232</v>
@@ -5445,16 +5645,16 @@
         <v>5</v>
       </c>
       <c r="O19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P19">
         <v>14</v>
       </c>
       <c r="Q19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="T19" t="s">
         <v>233</v>
@@ -5488,16 +5688,16 @@
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P20">
         <v>15</v>
       </c>
       <c r="Q20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="2:21">
@@ -5525,16 +5725,16 @@
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P21">
         <v>16</v>
       </c>
       <c r="Q21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="2:21">
@@ -5562,16 +5762,16 @@
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P22">
         <v>17</v>
       </c>
       <c r="Q22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="2:21">
@@ -5599,16 +5799,16 @@
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P23">
         <v>18</v>
       </c>
       <c r="Q23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="2:21">
@@ -5636,16 +5836,16 @@
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P24">
         <v>19</v>
       </c>
       <c r="Q24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="2:21">
@@ -5673,16 +5873,16 @@
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P25">
         <v>20</v>
       </c>
       <c r="Q25" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="2:21">
@@ -5710,16 +5910,16 @@
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P26">
         <v>21</v>
       </c>
       <c r="Q26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="2:21">
@@ -5747,16 +5947,16 @@
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P27">
         <v>22</v>
       </c>
       <c r="Q27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="2:21">
@@ -5784,16 +5984,16 @@
         <v>5</v>
       </c>
       <c r="O28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P28">
         <v>23</v>
       </c>
       <c r="Q28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="2:21">
@@ -5821,16 +6021,16 @@
         <v>5</v>
       </c>
       <c r="O29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P29">
         <v>24</v>
       </c>
       <c r="Q29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="2:21">
@@ -5858,16 +6058,16 @@
         <v>5</v>
       </c>
       <c r="O30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P30">
         <v>25</v>
       </c>
       <c r="Q30" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="2:21">
@@ -5895,16 +6095,16 @@
         <v>5</v>
       </c>
       <c r="O31" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P31">
         <v>26</v>
       </c>
       <c r="Q31" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R31" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="2:21">
@@ -5932,16 +6132,16 @@
         <v>5</v>
       </c>
       <c r="O32" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P32">
         <v>27</v>
       </c>
       <c r="Q32" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R32" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="2:18">
@@ -5969,16 +6169,16 @@
         <v>5</v>
       </c>
       <c r="O33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P33">
         <v>28</v>
       </c>
       <c r="Q33" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="2:18">
@@ -6006,16 +6206,16 @@
         <v>5</v>
       </c>
       <c r="O34" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P34">
         <v>29</v>
       </c>
       <c r="Q34" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="2:18">
@@ -6043,16 +6243,16 @@
         <v>5</v>
       </c>
       <c r="O35" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P35">
         <v>30</v>
       </c>
       <c r="Q35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R35" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="2:18">
@@ -6062,11 +6262,11 @@
       </c>
       <c r="C36" t="str">
         <f t="shared" si="5"/>
-        <v>e 1.5 deg no OS.f97p50</v>
+        <v>e 1.5 deg no OS.f96p50</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="2"/>
-        <v>e 1.5 deg no OS.f97p50</v>
+        <v>e 1.5 deg no OS.f96p50</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="3"/>
@@ -6074,22 +6274,22 @@
       </c>
       <c r="J36" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N36">
         <v>5</v>
       </c>
       <c r="O36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P36">
         <v>31</v>
       </c>
       <c r="Q36" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" spans="2:18">
@@ -6099,11 +6299,11 @@
       </c>
       <c r="C37" t="str">
         <f t="shared" si="5"/>
-        <v>d 1.5 deg OS.f97p50</v>
+        <v>d 1.5 deg OS.f96p50</v>
       </c>
       <c r="H37" t="str">
         <f t="shared" si="2"/>
-        <v>d 1.5 deg OS.f97p50</v>
+        <v>d 1.5 deg OS.f96p50</v>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="3"/>
@@ -6111,22 +6311,22 @@
       </c>
       <c r="J37" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N37">
         <v>5</v>
       </c>
       <c r="O37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P37">
         <v>32</v>
       </c>
       <c r="Q37" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R37" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="38" spans="2:18">
@@ -6136,11 +6336,11 @@
       </c>
       <c r="C38" t="str">
         <f t="shared" si="5"/>
-        <v>c 2 deg (67%).f97p50</v>
+        <v>c 2 deg (67%).f96p50</v>
       </c>
       <c r="H38" t="str">
         <f t="shared" si="2"/>
-        <v>c 2 deg (67%).f97p50</v>
+        <v>c 2 deg (67%).f96p50</v>
       </c>
       <c r="I38" t="str">
         <f t="shared" si="3"/>
@@ -6148,22 +6348,22 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N38">
         <v>5</v>
       </c>
       <c r="O38" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P38">
         <v>33</v>
       </c>
       <c r="Q38" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R38" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" spans="2:18">
@@ -6173,11 +6373,11 @@
       </c>
       <c r="C39" t="str">
         <f t="shared" si="5"/>
-        <v>b 2 deg (50%).f97p50</v>
+        <v>b 2 deg (50%).f96p50</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" si="2"/>
-        <v>b 2 deg (50%).f97p50</v>
+        <v>b 2 deg (50%).f96p50</v>
       </c>
       <c r="I39" t="str">
         <f t="shared" si="3"/>
@@ -6185,22 +6385,22 @@
       </c>
       <c r="J39" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N39">
         <v>5</v>
       </c>
       <c r="O39" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P39">
         <v>34</v>
       </c>
       <c r="Q39" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="2:18">
@@ -6210,11 +6410,11 @@
       </c>
       <c r="C40" t="str">
         <f t="shared" si="5"/>
-        <v>a 3 deg.f97p50</v>
+        <v>a 3 deg.f96p50</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" si="2"/>
-        <v>a 3 deg.f97p50</v>
+        <v>a 3 deg.f96p50</v>
       </c>
       <c r="I40" t="str">
         <f t="shared" si="3"/>
@@ -6222,22 +6422,22 @@
       </c>
       <c r="J40" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N40">
         <v>5</v>
       </c>
       <c r="O40" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P40">
         <v>35</v>
       </c>
       <c r="Q40" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="2:18">
@@ -6265,16 +6465,16 @@
         <v>5</v>
       </c>
       <c r="O41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P41">
         <v>36</v>
       </c>
       <c r="Q41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R41" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="2:18">
@@ -6302,16 +6502,16 @@
         <v>5</v>
       </c>
       <c r="O42" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P42">
         <v>37</v>
       </c>
       <c r="Q42" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R42" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="2:18">
@@ -6339,16 +6539,16 @@
         <v>5</v>
       </c>
       <c r="O43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P43">
         <v>38</v>
       </c>
       <c r="Q43" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="2:18">
@@ -6376,16 +6576,16 @@
         <v>5</v>
       </c>
       <c r="O44" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P44">
         <v>39</v>
       </c>
       <c r="Q44" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="2:18">
@@ -6413,16 +6613,16 @@
         <v>5</v>
       </c>
       <c r="O45" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P45">
         <v>40</v>
       </c>
       <c r="Q45" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R45" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="2:18">
@@ -6450,16 +6650,16 @@
         <v>5</v>
       </c>
       <c r="O46" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P46">
         <v>41</v>
       </c>
       <c r="Q46" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R46" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="2:18">
@@ -6487,16 +6687,16 @@
         <v>5</v>
       </c>
       <c r="O47" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P47">
         <v>42</v>
       </c>
       <c r="Q47" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48" spans="2:18">
@@ -6524,16 +6724,16 @@
         <v>5</v>
       </c>
       <c r="O48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P48">
         <v>43</v>
       </c>
       <c r="Q48" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="2:18">
@@ -6561,16 +6761,16 @@
         <v>5</v>
       </c>
       <c r="O49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P49">
         <v>44</v>
       </c>
       <c r="Q49" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R49" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="2:18">
@@ -6598,16 +6798,16 @@
         <v>5</v>
       </c>
       <c r="O50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P50">
         <v>45</v>
       </c>
       <c r="Q50" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R50" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="2:18">
@@ -6635,7 +6835,7 @@
         <v>5</v>
       </c>
       <c r="O51" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P51">
         <v>46</v>
@@ -6644,7 +6844,7 @@
         <v>230</v>
       </c>
       <c r="R51" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="2:18">
@@ -6672,7 +6872,7 @@
         <v>5</v>
       </c>
       <c r="O52" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P52">
         <v>47</v>
@@ -6681,7 +6881,7 @@
         <v>230</v>
       </c>
       <c r="R52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="2:18">
@@ -6709,7 +6909,7 @@
         <v>5</v>
       </c>
       <c r="O53" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P53">
         <v>48</v>
@@ -6718,7 +6918,7 @@
         <v>230</v>
       </c>
       <c r="R53" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" spans="2:18">
@@ -6746,7 +6946,7 @@
         <v>5</v>
       </c>
       <c r="O54" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P54">
         <v>49</v>
@@ -6755,7 +6955,7 @@
         <v>230</v>
       </c>
       <c r="R54" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="55" spans="2:18">
@@ -6783,7 +6983,7 @@
         <v>5</v>
       </c>
       <c r="O55" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P55">
         <v>50</v>
@@ -6792,7 +6992,7 @@
         <v>230</v>
       </c>
       <c r="R55" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="56" spans="2:18">
@@ -6820,7 +7020,7 @@
         <v>5</v>
       </c>
       <c r="O56" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P56">
         <v>51</v>
@@ -6829,7 +7029,7 @@
         <v>231</v>
       </c>
       <c r="R56" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="57" spans="2:18">
@@ -6857,7 +7057,7 @@
         <v>5</v>
       </c>
       <c r="O57" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P57">
         <v>52</v>
@@ -6866,7 +7066,7 @@
         <v>231</v>
       </c>
       <c r="R57" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="58" spans="2:18">
@@ -6894,7 +7094,7 @@
         <v>5</v>
       </c>
       <c r="O58" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P58">
         <v>53</v>
@@ -6903,7 +7103,7 @@
         <v>231</v>
       </c>
       <c r="R58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59" spans="2:18">
@@ -6931,7 +7131,7 @@
         <v>5</v>
       </c>
       <c r="O59" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P59">
         <v>54</v>
@@ -6940,7 +7140,7 @@
         <v>231</v>
       </c>
       <c r="R59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="2:18">
@@ -6968,7 +7168,7 @@
         <v>5</v>
       </c>
       <c r="O60" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P60">
         <v>55</v>
@@ -6977,7 +7177,7 @@
         <v>231</v>
       </c>
       <c r="R60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61" spans="2:18">
@@ -7005,7 +7205,7 @@
         <v>5</v>
       </c>
       <c r="O61" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P61">
         <v>56</v>
@@ -7014,7 +7214,7 @@
         <v>237</v>
       </c>
       <c r="R61" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62" spans="2:18">
@@ -7042,7 +7242,7 @@
         <v>5</v>
       </c>
       <c r="O62" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P62">
         <v>57</v>
@@ -7051,7 +7251,7 @@
         <v>237</v>
       </c>
       <c r="R62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="63" spans="2:18">
@@ -7079,7 +7279,7 @@
         <v>5</v>
       </c>
       <c r="O63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P63">
         <v>58</v>
@@ -7088,7 +7288,7 @@
         <v>237</v>
       </c>
       <c r="R63" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64" spans="2:18">
@@ -7116,7 +7316,7 @@
         <v>5</v>
       </c>
       <c r="O64" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P64">
         <v>59</v>
@@ -7125,7 +7325,7 @@
         <v>237</v>
       </c>
       <c r="R64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="65" spans="2:18">
@@ -7153,7 +7353,7 @@
         <v>5</v>
       </c>
       <c r="O65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P65">
         <v>60</v>
@@ -7162,7 +7362,7 @@
         <v>237</v>
       </c>
       <c r="R65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="2:18">
@@ -7190,7 +7390,7 @@
         <v>5</v>
       </c>
       <c r="O66" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P66">
         <v>61</v>
@@ -7199,7 +7399,7 @@
         <v>232</v>
       </c>
       <c r="R66" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="67" spans="2:18">
@@ -7227,7 +7427,7 @@
         <v>5</v>
       </c>
       <c r="O67" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P67">
         <v>62</v>
@@ -7236,7 +7436,7 @@
         <v>232</v>
       </c>
       <c r="R67" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="68" spans="2:18">
@@ -7264,7 +7464,7 @@
         <v>5</v>
       </c>
       <c r="O68" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P68">
         <v>63</v>
@@ -7273,7 +7473,7 @@
         <v>232</v>
       </c>
       <c r="R68" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69" spans="2:18">
@@ -7301,7 +7501,7 @@
         <v>5</v>
       </c>
       <c r="O69" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P69">
         <v>64</v>
@@ -7310,7 +7510,7 @@
         <v>232</v>
       </c>
       <c r="R69" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="70" spans="2:18">
@@ -7338,7 +7538,7 @@
         <v>5</v>
       </c>
       <c r="O70" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P70">
         <v>65</v>
@@ -7347,7 +7547,7 @@
         <v>232</v>
       </c>
       <c r="R70" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="2:18">
@@ -7375,7 +7575,7 @@
         <v>5</v>
       </c>
       <c r="O71" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P71">
         <v>66</v>
@@ -7384,7 +7584,7 @@
         <v>233</v>
       </c>
       <c r="R71" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="2:18">
@@ -7412,7 +7612,7 @@
         <v>5</v>
       </c>
       <c r="O72" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P72">
         <v>67</v>
@@ -7421,7 +7621,7 @@
         <v>233</v>
       </c>
       <c r="R72" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="73" spans="2:18">
@@ -7449,7 +7649,7 @@
         <v>5</v>
       </c>
       <c r="O73" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P73">
         <v>68</v>
@@ -7458,7 +7658,7 @@
         <v>233</v>
       </c>
       <c r="R73" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="74" spans="2:18">
@@ -7486,7 +7686,7 @@
         <v>5</v>
       </c>
       <c r="O74" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P74">
         <v>69</v>
@@ -7495,7 +7695,7 @@
         <v>233</v>
       </c>
       <c r="R74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75" spans="2:18">
@@ -7523,7 +7723,7 @@
         <v>5</v>
       </c>
       <c r="O75" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P75">
         <v>70</v>
@@ -7532,7 +7732,7 @@
         <v>233</v>
       </c>
       <c r="R75" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -7548,7 +7748,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -7685,7 +7885,7 @@
         <v>157</v>
       </c>
       <c r="I5" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="K5" t="s">
         <v>80</v>
@@ -7769,7 +7969,7 @@
         <v>117</v>
       </c>
       <c r="K9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N9" t="s">
         <v>82</v>
@@ -7851,13 +8051,13 @@
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K14" t="s">
+        <v>291</v>
+      </c>
+      <c r="N14" t="s">
         <v>292</v>
-      </c>
-      <c r="N14" t="s">
-        <v>293</v>
       </c>
       <c r="Q14" t="s">
         <v>50</v>
@@ -7865,16 +8065,107 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K15" t="s">
         <v>291</v>
       </c>
-      <c r="K15" t="s">
-        <v>292</v>
-      </c>
       <c r="N15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q15" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>388</v>
+      </c>
+      <c r="D16" t="s">
+        <v>389</v>
+      </c>
+      <c r="K16" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>388</v>
+      </c>
+      <c r="D17" t="s">
+        <v>389</v>
+      </c>
+      <c r="K17" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" t="s">
+        <v>397</v>
+      </c>
+      <c r="I18" t="s">
+        <v>398</v>
+      </c>
+      <c r="K18" t="s">
+        <v>80</v>
+      </c>
+      <c r="N18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" t="s">
+        <v>161</v>
+      </c>
+      <c r="I19" t="s">
+        <v>403</v>
+      </c>
+      <c r="K19" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" t="s">
+        <v>399</v>
+      </c>
+      <c r="P19" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" t="s">
+        <v>403</v>
+      </c>
+      <c r="K20" t="s">
+        <v>80</v>
+      </c>
+      <c r="N20" t="s">
+        <v>402</v>
+      </c>
+      <c r="P20" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -7976,7 +8267,7 @@
   <sheetData>
     <row r="3" spans="1:19" ht="17.25" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" thickTop="1" thickBot="1">
@@ -8084,7 +8375,7 @@
     </row>
     <row r="10" spans="1:19" ht="17.25" thickBot="1">
       <c r="A10" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" thickTop="1" thickBot="1">
@@ -8151,7 +8442,7 @@
         <v>120</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -8170,7 +8461,7 @@
         <v>160</v>
       </c>
       <c r="M13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -8192,7 +8483,7 @@
         <v>160</v>
       </c>
       <c r="M14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -8203,7 +8494,7 @@
         <v>120</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -8222,7 +8513,7 @@
         <v>160</v>
       </c>
       <c r="M16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -8244,7 +8535,7 @@
         <v>160</v>
       </c>
       <c r="M17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -8255,7 +8546,7 @@
         <v>120</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -8273,7 +8564,7 @@
         <v>160</v>
       </c>
       <c r="M19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -8294,7 +8585,7 @@
         <v>160</v>
       </c>
       <c r="M20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -8314,7 +8605,7 @@
         <v>160</v>
       </c>
       <c r="M23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -8438,7 +8729,7 @@
         <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -8446,7 +8737,7 @@
         <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -8979,7 +9270,7 @@
         <v>202</v>
       </c>
       <c r="B24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -8987,7 +9278,7 @@
         <v>203</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9004,7 +9295,7 @@
         <v>187</v>
       </c>
       <c r="B27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9141,7 +9432,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
@@ -9150,7 +9441,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
@@ -9177,7 +9468,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
@@ -9186,7 +9477,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
@@ -9195,18 +9486,18 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
